--- a/data/Finland_resampling2025_ID.xlsx
+++ b/data/Finland_resampling2025_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ad.helsinki.fi\home\g\gerargsy\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D12D64-D5F4-4E9D-B1A3-8D91C0AD7D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6939BA24-4470-4601-8A15-2F59C5912F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="13840" windowHeight="11370" xr2:uid="{62381CB3-6983-4B4B-80E0-EF394FFF3EEF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{62381CB3-6983-4B4B-80E0-EF394FFF3EEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8347" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9996" uniqueCount="1270">
   <si>
     <t>specimen_name</t>
   </si>
@@ -3267,6 +3267,588 @@
   </si>
   <si>
     <t>SG_viikki_0570</t>
+  </si>
+  <si>
+    <t>Tvarminne_34</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_1</t>
+  </si>
+  <si>
+    <t>SG_viikki_0571</t>
+  </si>
+  <si>
+    <t>SG_viikki_0572</t>
+  </si>
+  <si>
+    <t>SG_viikki_0573</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_2</t>
+  </si>
+  <si>
+    <t>SG_viikki_0574</t>
+  </si>
+  <si>
+    <t>endogeic</t>
+  </si>
+  <si>
+    <t>SG_viikki_0575</t>
+  </si>
+  <si>
+    <t>SG_viikki_0576</t>
+  </si>
+  <si>
+    <t>SG_viikki_0577</t>
+  </si>
+  <si>
+    <t>SG_viikki_0578</t>
+  </si>
+  <si>
+    <t>SG_viikki_0579</t>
+  </si>
+  <si>
+    <t>SG_viikki_0580</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_3</t>
+  </si>
+  <si>
+    <t>SG_viikki_0581</t>
+  </si>
+  <si>
+    <t>SG_viikki_0582</t>
+  </si>
+  <si>
+    <t>SG_viikki_0583</t>
+  </si>
+  <si>
+    <t>SG_viikki_0584</t>
+  </si>
+  <si>
+    <t>SG_viikki_0585</t>
+  </si>
+  <si>
+    <t>SG_viikki_0586</t>
+  </si>
+  <si>
+    <t>SG_viikki_0587</t>
+  </si>
+  <si>
+    <t>SG_viikki_0588</t>
+  </si>
+  <si>
+    <t>SG_viikki_0589</t>
+  </si>
+  <si>
+    <t>SG_viikki_0590</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_4</t>
+  </si>
+  <si>
+    <t>SG_viikki_0591</t>
+  </si>
+  <si>
+    <t>SG_viikki_0592</t>
+  </si>
+  <si>
+    <t>SG_viikki_0593</t>
+  </si>
+  <si>
+    <t>SG_viikki_0594</t>
+  </si>
+  <si>
+    <t>SG_viikki_0595</t>
+  </si>
+  <si>
+    <t>SG_viikki_0596</t>
+  </si>
+  <si>
+    <t>SG_viikki_0597</t>
+  </si>
+  <si>
+    <t>probably L. terrestris</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_5</t>
+  </si>
+  <si>
+    <t>SG_viikki_0598</t>
+  </si>
+  <si>
+    <t>Lumbricus castaneus</t>
+  </si>
+  <si>
+    <t>SG_viikki_0599</t>
+  </si>
+  <si>
+    <t>SG_viikki_0600</t>
+  </si>
+  <si>
+    <t>SG_viikki_0601</t>
+  </si>
+  <si>
+    <t>SG_viikki_0602</t>
+  </si>
+  <si>
+    <t>SG_viikki_0603</t>
+  </si>
+  <si>
+    <t>SG_viikki_0604</t>
+  </si>
+  <si>
+    <t>SG_viikki_0605</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_6</t>
+  </si>
+  <si>
+    <t>SG_viikki_0606</t>
+  </si>
+  <si>
+    <t>SG_viikki_0607</t>
+  </si>
+  <si>
+    <t>SG_viikki_0608</t>
+  </si>
+  <si>
+    <t>SG_viikki_0609</t>
+  </si>
+  <si>
+    <t>SG_viikki_0610</t>
+  </si>
+  <si>
+    <t>SG_viikki_0611</t>
+  </si>
+  <si>
+    <t>SG_viikki_0612</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_7</t>
+  </si>
+  <si>
+    <t>SG_viikki_0613</t>
+  </si>
+  <si>
+    <t>SG_viikki_0614</t>
+  </si>
+  <si>
+    <t>SG_viikki_0615</t>
+  </si>
+  <si>
+    <t>SG_viikki_0616</t>
+  </si>
+  <si>
+    <t>SG_viikki_0617</t>
+  </si>
+  <si>
+    <t>SG_viikki_0618</t>
+  </si>
+  <si>
+    <t>SG_viikki_0619</t>
+  </si>
+  <si>
+    <t>SG_viikki_0620</t>
+  </si>
+  <si>
+    <t>SG_viikki_0621</t>
+  </si>
+  <si>
+    <t>SG_viikki_0622</t>
+  </si>
+  <si>
+    <t>SG_viikki_0623</t>
+  </si>
+  <si>
+    <t>SG_viikki_0624</t>
+  </si>
+  <si>
+    <t>SG_viikki_0625</t>
+  </si>
+  <si>
+    <t>SG_viikki_0626</t>
+  </si>
+  <si>
+    <t>SG_viikki_0627</t>
+  </si>
+  <si>
+    <t>SG_viikki_0628</t>
+  </si>
+  <si>
+    <t>SG_viikki_0629</t>
+  </si>
+  <si>
+    <t>SG_viikki_0630</t>
+  </si>
+  <si>
+    <t>SG_viikki_0631</t>
+  </si>
+  <si>
+    <t>SG_viikki_0632</t>
+  </si>
+  <si>
+    <t>SG_viikki_0633</t>
+  </si>
+  <si>
+    <t>SG_viikki_0634</t>
+  </si>
+  <si>
+    <t>SG_viikki_0635</t>
+  </si>
+  <si>
+    <t>SG_viikki_0636</t>
+  </si>
+  <si>
+    <t>SG_viikki_0637</t>
+  </si>
+  <si>
+    <t>SG_viikki_0638</t>
+  </si>
+  <si>
+    <t>SG_viikki_0639</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_8</t>
+  </si>
+  <si>
+    <t>SG_viikki_0640</t>
+  </si>
+  <si>
+    <t>SG_viikki_0641</t>
+  </si>
+  <si>
+    <t>SG_viikki_0642</t>
+  </si>
+  <si>
+    <t>SG_viikki_0643</t>
+  </si>
+  <si>
+    <t>SG_viikki_0644</t>
+  </si>
+  <si>
+    <t>SG_viikki_0645</t>
+  </si>
+  <si>
+    <t>SG_viikki_0646</t>
+  </si>
+  <si>
+    <t>SG_viikki_0647</t>
+  </si>
+  <si>
+    <t>SG_viikki_0648</t>
+  </si>
+  <si>
+    <t>SG_viikki_0649</t>
+  </si>
+  <si>
+    <t>SG_viikki_0650</t>
+  </si>
+  <si>
+    <t>SG_viikki_0651</t>
+  </si>
+  <si>
+    <t>SG_viikki_0652</t>
+  </si>
+  <si>
+    <t>SG_viikki_0653</t>
+  </si>
+  <si>
+    <t>SG_viikki_0654</t>
+  </si>
+  <si>
+    <t>Tvarminne_34_9</t>
+  </si>
+  <si>
+    <t>SG_viikki_0655</t>
+  </si>
+  <si>
+    <t>SG_viikki_0656</t>
+  </si>
+  <si>
+    <t>SG_viikki_0657</t>
+  </si>
+  <si>
+    <t>SG_viikki_0658</t>
+  </si>
+  <si>
+    <t>SG_viikki_0659</t>
+  </si>
+  <si>
+    <t>SG_viikki_0660</t>
+  </si>
+  <si>
+    <t>SG_viikki_0661</t>
+  </si>
+  <si>
+    <t>SG_viikki_0662</t>
+  </si>
+  <si>
+    <t>SG_viikki_0663</t>
+  </si>
+  <si>
+    <t>SG_viikki_0664</t>
+  </si>
+  <si>
+    <t>SG_viikki_0665</t>
+  </si>
+  <si>
+    <t>SG_viikki_0666</t>
+  </si>
+  <si>
+    <t>SG_viikki_0667</t>
+  </si>
+  <si>
+    <t>SG_viikki_0668</t>
+  </si>
+  <si>
+    <t>SG_viikki_0669</t>
+  </si>
+  <si>
+    <t>SG_viikki_0670</t>
+  </si>
+  <si>
+    <t>SG_viikki_0671</t>
+  </si>
+  <si>
+    <t>SG_viikki_0672</t>
+  </si>
+  <si>
+    <t>SG_viikki_0673</t>
+  </si>
+  <si>
+    <t>SG_viikki_0674</t>
+  </si>
+  <si>
+    <t>SG_viikki_0675</t>
+  </si>
+  <si>
+    <t>SG_viikki_0676</t>
+  </si>
+  <si>
+    <t>SG_viikki_0677</t>
+  </si>
+  <si>
+    <t>SG_viikki_0678</t>
+  </si>
+  <si>
+    <t>SG_viikki_0679</t>
+  </si>
+  <si>
+    <t>SG_viikki_0680</t>
+  </si>
+  <si>
+    <t>SG_viikki_0681</t>
+  </si>
+  <si>
+    <t>SG_viikki_0682</t>
+  </si>
+  <si>
+    <t>SG_viikki_0683</t>
+  </si>
+  <si>
+    <t>SG_viikki_0684</t>
+  </si>
+  <si>
+    <t>SG_viikki_0685</t>
+  </si>
+  <si>
+    <t>SG_viikki_0686</t>
+  </si>
+  <si>
+    <t>SG_viikki_0687</t>
+  </si>
+  <si>
+    <t>SG_viikki_0688</t>
+  </si>
+  <si>
+    <t>SG_viikki_0689</t>
+  </si>
+  <si>
+    <t>SG_viikki_0690</t>
+  </si>
+  <si>
+    <t>SG_viikki_0691</t>
+  </si>
+  <si>
+    <t>Tvarminne_61</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_1</t>
+  </si>
+  <si>
+    <t>Octolasion</t>
+  </si>
+  <si>
+    <t>SG_viikki_0692</t>
+  </si>
+  <si>
+    <t>SG_viikki_0693</t>
+  </si>
+  <si>
+    <t>SG_viikki_0694</t>
+  </si>
+  <si>
+    <t>SG_viikki_0695</t>
+  </si>
+  <si>
+    <t>SG_viikki_0696</t>
+  </si>
+  <si>
+    <t>SG_viikki_0697</t>
+  </si>
+  <si>
+    <t>SG_viikki_0698</t>
+  </si>
+  <si>
+    <t>SG_viikki_0699</t>
+  </si>
+  <si>
+    <t>prob Aporrectodea</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_2</t>
+  </si>
+  <si>
+    <t>SG_viikki_0700</t>
+  </si>
+  <si>
+    <t>SG_viikki_0701</t>
+  </si>
+  <si>
+    <t>SG_viikki_0702</t>
+  </si>
+  <si>
+    <t>SG_viikki_0703</t>
+  </si>
+  <si>
+    <t>SG_viikki_0704</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_3</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_4</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_5</t>
+  </si>
+  <si>
+    <t>SG_viikki_0705</t>
+  </si>
+  <si>
+    <t>SG_viikki_0706</t>
+  </si>
+  <si>
+    <t>SG_viikki_0707</t>
+  </si>
+  <si>
+    <t>SG_viikki_0708</t>
+  </si>
+  <si>
+    <t>SG_viikki_0709</t>
+  </si>
+  <si>
+    <t>SG_viikki_0710</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_6</t>
+  </si>
+  <si>
+    <t>SG_viikki_0711</t>
+  </si>
+  <si>
+    <t>SG_viikki_0712</t>
+  </si>
+  <si>
+    <t>prob L terrestris</t>
+  </si>
+  <si>
+    <t>SG_viikki_0713</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_7</t>
+  </si>
+  <si>
+    <t>Octolasion lacteum</t>
+  </si>
+  <si>
+    <t>tyrtaeum morph</t>
+  </si>
+  <si>
+    <t>SG_viikki_0714</t>
+  </si>
+  <si>
+    <t>SG_viikki_0715</t>
+  </si>
+  <si>
+    <t>SG_viikki_0716</t>
+  </si>
+  <si>
+    <t>SG_viikki_0717</t>
+  </si>
+  <si>
+    <t>SG_viikki_0718</t>
+  </si>
+  <si>
+    <t>SG_viikki_0719</t>
+  </si>
+  <si>
+    <t>SG_viikki_0720</t>
+  </si>
+  <si>
+    <t>SG_viikki_0721</t>
+  </si>
+  <si>
+    <t>SG_viikki_0722</t>
+  </si>
+  <si>
+    <t>SG_viikki_0723</t>
+  </si>
+  <si>
+    <t>SG_viikki_0724</t>
+  </si>
+  <si>
+    <t>SG_viikki_0725</t>
+  </si>
+  <si>
+    <t>SG_viikki_0726</t>
+  </si>
+  <si>
+    <t>SG_viikki_0727</t>
+  </si>
+  <si>
+    <t>SG_viikki_0728</t>
+  </si>
+  <si>
+    <t>SG_viikki_0729</t>
+  </si>
+  <si>
+    <t>SG_viikki_0730</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_8</t>
+  </si>
+  <si>
+    <t>SG_viikki_0731</t>
+  </si>
+  <si>
+    <t>SG_viikki_0732</t>
+  </si>
+  <si>
+    <t>SG_viikki_0733</t>
+  </si>
+  <si>
+    <t>SG_viikki_0734</t>
+  </si>
+  <si>
+    <t>Tvarminne_61_9</t>
+  </si>
+  <si>
+    <t>SG_viikki_0735</t>
+  </si>
+  <si>
+    <t>SG_viikki_0736</t>
   </si>
 </sst>
 </file>
@@ -3652,7 +4234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCF7B1D-30EB-41FA-B0BA-2D9928994D79}">
-  <dimension ref="A1:O768"/>
+  <dimension ref="A1:O945"/>
   <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
@@ -33281,6 +33863,9 @@
       <c r="M738" t="s">
         <v>887</v>
       </c>
+      <c r="N738" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="739" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
@@ -34434,6 +35019,6831 @@
         <v>15</v>
       </c>
       <c r="N768" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="769" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A769" t="s">
+        <v>887</v>
+      </c>
+      <c r="B769" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C769" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D769" t="s">
+        <v>21</v>
+      </c>
+      <c r="E769" t="s">
+        <v>887</v>
+      </c>
+      <c r="F769" t="s">
+        <v>887</v>
+      </c>
+      <c r="G769" t="s">
+        <v>887</v>
+      </c>
+      <c r="H769" t="s">
+        <v>887</v>
+      </c>
+      <c r="I769">
+        <v>0</v>
+      </c>
+      <c r="J769" t="s">
+        <v>887</v>
+      </c>
+      <c r="K769" t="s">
+        <v>886</v>
+      </c>
+      <c r="L769" t="s">
+        <v>887</v>
+      </c>
+      <c r="M769" t="s">
+        <v>887</v>
+      </c>
+      <c r="N769" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="770" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A770" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B770" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C770" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D770" t="s">
+        <v>60</v>
+      </c>
+      <c r="E770" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F770" t="s">
+        <v>12</v>
+      </c>
+      <c r="G770" t="s">
+        <v>13</v>
+      </c>
+      <c r="H770">
+        <v>4.6719999999999997</v>
+      </c>
+      <c r="I770">
+        <v>1</v>
+      </c>
+      <c r="L770">
+        <v>20260515</v>
+      </c>
+      <c r="M770" t="s">
+        <v>15</v>
+      </c>
+      <c r="N770" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A771" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C771" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D771" t="s">
+        <v>60</v>
+      </c>
+      <c r="E771" t="s">
+        <v>18</v>
+      </c>
+      <c r="F771" t="s">
+        <v>12</v>
+      </c>
+      <c r="G771" t="s">
+        <v>13</v>
+      </c>
+      <c r="H771">
+        <v>1.302</v>
+      </c>
+      <c r="I771">
+        <v>1</v>
+      </c>
+      <c r="L771">
+        <v>20260515</v>
+      </c>
+      <c r="M771" t="s">
+        <v>15</v>
+      </c>
+      <c r="N771" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="772" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A772" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B772" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C772" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D772" t="s">
+        <v>60</v>
+      </c>
+      <c r="E772" t="s">
+        <v>27</v>
+      </c>
+      <c r="F772" t="s">
+        <v>22</v>
+      </c>
+      <c r="G772" t="s">
+        <v>13</v>
+      </c>
+      <c r="H772">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I772">
+        <v>1</v>
+      </c>
+      <c r="L772">
+        <v>20260515</v>
+      </c>
+      <c r="M772" t="s">
+        <v>15</v>
+      </c>
+      <c r="N772" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="773" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A773" t="s">
+        <v>887</v>
+      </c>
+      <c r="B773" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C773" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D773" t="s">
+        <v>21</v>
+      </c>
+      <c r="E773" t="s">
+        <v>887</v>
+      </c>
+      <c r="F773" t="s">
+        <v>887</v>
+      </c>
+      <c r="G773" t="s">
+        <v>887</v>
+      </c>
+      <c r="H773" t="s">
+        <v>887</v>
+      </c>
+      <c r="I773">
+        <v>0</v>
+      </c>
+      <c r="J773" t="s">
+        <v>887</v>
+      </c>
+      <c r="K773" t="s">
+        <v>886</v>
+      </c>
+      <c r="L773" t="s">
+        <v>887</v>
+      </c>
+      <c r="M773" t="s">
+        <v>887</v>
+      </c>
+      <c r="N773" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="774" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A774" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C774" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D774" t="s">
+        <v>60</v>
+      </c>
+      <c r="E774" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F774" t="s">
+        <v>12</v>
+      </c>
+      <c r="G774" t="s">
+        <v>13</v>
+      </c>
+      <c r="H774">
+        <v>4.3419999999999996</v>
+      </c>
+      <c r="I774">
+        <v>1</v>
+      </c>
+      <c r="L774">
+        <v>20260515</v>
+      </c>
+      <c r="M774" t="s">
+        <v>15</v>
+      </c>
+      <c r="N774" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="775" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A775" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C775" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D775" t="s">
+        <v>60</v>
+      </c>
+      <c r="E775" t="s">
+        <v>79</v>
+      </c>
+      <c r="F775" t="s">
+        <v>22</v>
+      </c>
+      <c r="G775" t="s">
+        <v>13</v>
+      </c>
+      <c r="H775">
+        <v>0.185</v>
+      </c>
+      <c r="I775">
+        <v>1</v>
+      </c>
+      <c r="L775">
+        <v>20260515</v>
+      </c>
+      <c r="M775" t="s">
+        <v>15</v>
+      </c>
+      <c r="N775" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="776" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A776" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B776" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C776" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D776" t="s">
+        <v>60</v>
+      </c>
+      <c r="E776" t="s">
+        <v>79</v>
+      </c>
+      <c r="F776" t="s">
+        <v>22</v>
+      </c>
+      <c r="G776" t="s">
+        <v>13</v>
+      </c>
+      <c r="H776">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="I776">
+        <v>1</v>
+      </c>
+      <c r="L776">
+        <v>20260515</v>
+      </c>
+      <c r="M776" t="s">
+        <v>15</v>
+      </c>
+      <c r="N776" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="777" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A777" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B777" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C777" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D777" t="s">
+        <v>60</v>
+      </c>
+      <c r="E777" t="s">
+        <v>79</v>
+      </c>
+      <c r="F777" t="s">
+        <v>22</v>
+      </c>
+      <c r="G777" t="s">
+        <v>13</v>
+      </c>
+      <c r="H777">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I777">
+        <v>1</v>
+      </c>
+      <c r="L777">
+        <v>20260515</v>
+      </c>
+      <c r="M777" t="s">
+        <v>15</v>
+      </c>
+      <c r="N777" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="778" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A778" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B778" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C778" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D778" t="s">
+        <v>60</v>
+      </c>
+      <c r="E778" t="s">
+        <v>79</v>
+      </c>
+      <c r="F778" t="s">
+        <v>22</v>
+      </c>
+      <c r="G778" t="s">
+        <v>13</v>
+      </c>
+      <c r="H778">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="I778">
+        <v>1</v>
+      </c>
+      <c r="L778">
+        <v>20260515</v>
+      </c>
+      <c r="M778" t="s">
+        <v>15</v>
+      </c>
+      <c r="N778" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="779" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A779" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B779" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C779" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D779" t="s">
+        <v>60</v>
+      </c>
+      <c r="E779" t="s">
+        <v>79</v>
+      </c>
+      <c r="F779" t="s">
+        <v>22</v>
+      </c>
+      <c r="G779" t="s">
+        <v>13</v>
+      </c>
+      <c r="H779">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I779">
+        <v>1</v>
+      </c>
+      <c r="L779">
+        <v>20260515</v>
+      </c>
+      <c r="M779" t="s">
+        <v>15</v>
+      </c>
+      <c r="N779" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="780" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A780" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B780" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C780" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D780" t="s">
+        <v>60</v>
+      </c>
+      <c r="E780" t="s">
+        <v>45</v>
+      </c>
+      <c r="F780" t="s">
+        <v>22</v>
+      </c>
+      <c r="G780" t="s">
+        <v>13</v>
+      </c>
+      <c r="H780">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="I780">
+        <v>1</v>
+      </c>
+      <c r="J780" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L780">
+        <v>20260515</v>
+      </c>
+      <c r="M780" t="s">
+        <v>15</v>
+      </c>
+      <c r="N780" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="781" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A781" t="s">
+        <v>887</v>
+      </c>
+      <c r="B781" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C781" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D781" t="s">
+        <v>21</v>
+      </c>
+      <c r="E781" t="s">
+        <v>887</v>
+      </c>
+      <c r="F781" t="s">
+        <v>887</v>
+      </c>
+      <c r="G781" t="s">
+        <v>887</v>
+      </c>
+      <c r="H781" t="s">
+        <v>887</v>
+      </c>
+      <c r="I781">
+        <v>0</v>
+      </c>
+      <c r="J781" t="s">
+        <v>887</v>
+      </c>
+      <c r="K781" t="s">
+        <v>886</v>
+      </c>
+      <c r="L781" t="s">
+        <v>887</v>
+      </c>
+      <c r="M781" t="s">
+        <v>887</v>
+      </c>
+      <c r="N781" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="782" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A782" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B782" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C782" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D782" t="s">
+        <v>60</v>
+      </c>
+      <c r="E782" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F782" t="s">
+        <v>12</v>
+      </c>
+      <c r="G782" t="s">
+        <v>13</v>
+      </c>
+      <c r="H782">
+        <v>3.4790000000000001</v>
+      </c>
+      <c r="I782">
+        <v>1</v>
+      </c>
+      <c r="L782">
+        <v>20260515</v>
+      </c>
+      <c r="M782" t="s">
+        <v>15</v>
+      </c>
+      <c r="N782" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="783" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A783" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B783" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C783" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D783" t="s">
+        <v>60</v>
+      </c>
+      <c r="E783" t="s">
+        <v>18</v>
+      </c>
+      <c r="F783" t="s">
+        <v>16</v>
+      </c>
+      <c r="G783" t="s">
+        <v>13</v>
+      </c>
+      <c r="H783">
+        <v>0.625</v>
+      </c>
+      <c r="I783">
+        <v>1</v>
+      </c>
+      <c r="L783">
+        <v>20260515</v>
+      </c>
+      <c r="M783" t="s">
+        <v>15</v>
+      </c>
+      <c r="N783" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="784" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A784" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B784" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C784" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D784" t="s">
+        <v>60</v>
+      </c>
+      <c r="E784" t="s">
+        <v>17</v>
+      </c>
+      <c r="F784" t="s">
+        <v>16</v>
+      </c>
+      <c r="G784" t="s">
+        <v>13</v>
+      </c>
+      <c r="H784">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="I784">
+        <v>1</v>
+      </c>
+      <c r="L784">
+        <v>20260515</v>
+      </c>
+      <c r="M784" t="s">
+        <v>15</v>
+      </c>
+      <c r="N784" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="785" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A785" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B785" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C785" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D785" t="s">
+        <v>60</v>
+      </c>
+      <c r="E785" t="s">
+        <v>79</v>
+      </c>
+      <c r="F785" t="s">
+        <v>22</v>
+      </c>
+      <c r="G785" t="s">
+        <v>13</v>
+      </c>
+      <c r="H785">
+        <v>2.7E-2</v>
+      </c>
+      <c r="I785">
+        <v>1</v>
+      </c>
+      <c r="L785">
+        <v>20260515</v>
+      </c>
+      <c r="M785" t="s">
+        <v>15</v>
+      </c>
+      <c r="N785" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="786" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A786" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B786" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C786" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D786" t="s">
+        <v>60</v>
+      </c>
+      <c r="E786" t="s">
+        <v>79</v>
+      </c>
+      <c r="F786" t="s">
+        <v>22</v>
+      </c>
+      <c r="G786" t="s">
+        <v>13</v>
+      </c>
+      <c r="H786">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I786">
+        <v>1</v>
+      </c>
+      <c r="L786">
+        <v>20260515</v>
+      </c>
+      <c r="M786" t="s">
+        <v>15</v>
+      </c>
+      <c r="N786" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="787" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A787" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B787" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C787" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D787" t="s">
+        <v>60</v>
+      </c>
+      <c r="E787" t="s">
+        <v>79</v>
+      </c>
+      <c r="F787" t="s">
+        <v>22</v>
+      </c>
+      <c r="G787" t="s">
+        <v>13</v>
+      </c>
+      <c r="H787">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I787">
+        <v>1</v>
+      </c>
+      <c r="L787">
+        <v>20260515</v>
+      </c>
+      <c r="M787" t="s">
+        <v>15</v>
+      </c>
+      <c r="N787" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="788" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A788" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B788" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C788" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D788" t="s">
+        <v>60</v>
+      </c>
+      <c r="E788" t="s">
+        <v>79</v>
+      </c>
+      <c r="F788" t="s">
+        <v>22</v>
+      </c>
+      <c r="G788" t="s">
+        <v>13</v>
+      </c>
+      <c r="H788">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I788">
+        <v>1</v>
+      </c>
+      <c r="L788">
+        <v>20260515</v>
+      </c>
+      <c r="M788" t="s">
+        <v>15</v>
+      </c>
+      <c r="N788" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="789" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A789" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B789" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C789" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D789" t="s">
+        <v>60</v>
+      </c>
+      <c r="E789" t="s">
+        <v>79</v>
+      </c>
+      <c r="F789" t="s">
+        <v>22</v>
+      </c>
+      <c r="G789" t="s">
+        <v>13</v>
+      </c>
+      <c r="H789">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I789">
+        <v>1</v>
+      </c>
+      <c r="L789">
+        <v>20260515</v>
+      </c>
+      <c r="M789" t="s">
+        <v>15</v>
+      </c>
+      <c r="N789" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="790" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A790" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B790" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C790" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D790" t="s">
+        <v>60</v>
+      </c>
+      <c r="E790" t="s">
+        <v>45</v>
+      </c>
+      <c r="F790" t="s">
+        <v>22</v>
+      </c>
+      <c r="G790" t="s">
+        <v>13</v>
+      </c>
+      <c r="H790">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I790">
+        <v>1</v>
+      </c>
+      <c r="L790">
+        <v>20260515</v>
+      </c>
+      <c r="M790" t="s">
+        <v>15</v>
+      </c>
+      <c r="N790" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="791" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A791" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B791" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C791" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D791" t="s">
+        <v>60</v>
+      </c>
+      <c r="E791" t="s">
+        <v>45</v>
+      </c>
+      <c r="F791" t="s">
+        <v>22</v>
+      </c>
+      <c r="G791" t="s">
+        <v>13</v>
+      </c>
+      <c r="H791">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I791">
+        <v>1</v>
+      </c>
+      <c r="L791">
+        <v>20260515</v>
+      </c>
+      <c r="M791" t="s">
+        <v>15</v>
+      </c>
+      <c r="N791" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="792" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A792" t="s">
+        <v>887</v>
+      </c>
+      <c r="B792" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C792" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D792" t="s">
+        <v>21</v>
+      </c>
+      <c r="E792" t="s">
+        <v>887</v>
+      </c>
+      <c r="F792" t="s">
+        <v>887</v>
+      </c>
+      <c r="G792" t="s">
+        <v>887</v>
+      </c>
+      <c r="H792" t="s">
+        <v>887</v>
+      </c>
+      <c r="I792">
+        <v>0</v>
+      </c>
+      <c r="J792" t="s">
+        <v>887</v>
+      </c>
+      <c r="K792" t="s">
+        <v>886</v>
+      </c>
+      <c r="L792" t="s">
+        <v>887</v>
+      </c>
+      <c r="M792" t="s">
+        <v>887</v>
+      </c>
+      <c r="N792" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="793" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A793" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B793" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C793" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D793" t="s">
+        <v>60</v>
+      </c>
+      <c r="E793" t="s">
+        <v>18</v>
+      </c>
+      <c r="F793" t="s">
+        <v>12</v>
+      </c>
+      <c r="G793" t="s">
+        <v>13</v>
+      </c>
+      <c r="H793">
+        <v>0.318</v>
+      </c>
+      <c r="I793">
+        <v>1</v>
+      </c>
+      <c r="L793">
+        <v>20260515</v>
+      </c>
+      <c r="M793" t="s">
+        <v>15</v>
+      </c>
+      <c r="N793" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="794" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A794" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C794" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D794" t="s">
+        <v>60</v>
+      </c>
+      <c r="E794" t="s">
+        <v>17</v>
+      </c>
+      <c r="F794" t="s">
+        <v>16</v>
+      </c>
+      <c r="G794" t="s">
+        <v>13</v>
+      </c>
+      <c r="H794">
+        <v>0.151</v>
+      </c>
+      <c r="I794">
+        <v>1</v>
+      </c>
+      <c r="L794">
+        <v>20260515</v>
+      </c>
+      <c r="M794" t="s">
+        <v>15</v>
+      </c>
+      <c r="N794" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="795" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A795" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C795" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D795" t="s">
+        <v>60</v>
+      </c>
+      <c r="E795" t="s">
+        <v>27</v>
+      </c>
+      <c r="F795" t="s">
+        <v>22</v>
+      </c>
+      <c r="G795" t="s">
+        <v>13</v>
+      </c>
+      <c r="H795">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="I795">
+        <v>1</v>
+      </c>
+      <c r="L795">
+        <v>20260515</v>
+      </c>
+      <c r="M795" t="s">
+        <v>15</v>
+      </c>
+      <c r="N795" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A796" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C796" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D796" t="s">
+        <v>60</v>
+      </c>
+      <c r="E796" t="s">
+        <v>79</v>
+      </c>
+      <c r="F796" t="s">
+        <v>22</v>
+      </c>
+      <c r="G796" t="s">
+        <v>13</v>
+      </c>
+      <c r="H796">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="I796">
+        <v>1</v>
+      </c>
+      <c r="J796" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L796">
+        <v>20260515</v>
+      </c>
+      <c r="M796" t="s">
+        <v>15</v>
+      </c>
+      <c r="N796" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="797" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A797" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C797" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D797" t="s">
+        <v>60</v>
+      </c>
+      <c r="E797" t="s">
+        <v>79</v>
+      </c>
+      <c r="F797" t="s">
+        <v>22</v>
+      </c>
+      <c r="G797" t="s">
+        <v>13</v>
+      </c>
+      <c r="H797">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I797">
+        <v>1</v>
+      </c>
+      <c r="L797">
+        <v>20260515</v>
+      </c>
+      <c r="M797" t="s">
+        <v>15</v>
+      </c>
+      <c r="N797" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="798" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A798" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B798" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C798" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D798" t="s">
+        <v>60</v>
+      </c>
+      <c r="E798" t="s">
+        <v>79</v>
+      </c>
+      <c r="F798" t="s">
+        <v>22</v>
+      </c>
+      <c r="G798" t="s">
+        <v>13</v>
+      </c>
+      <c r="H798">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I798">
+        <v>1</v>
+      </c>
+      <c r="L798">
+        <v>20260515</v>
+      </c>
+      <c r="M798" t="s">
+        <v>15</v>
+      </c>
+      <c r="N798" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="799" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A799" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B799" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C799" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D799" t="s">
+        <v>60</v>
+      </c>
+      <c r="E799" t="s">
+        <v>45</v>
+      </c>
+      <c r="F799" t="s">
+        <v>22</v>
+      </c>
+      <c r="G799" t="s">
+        <v>13</v>
+      </c>
+      <c r="H799">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I799">
+        <v>1</v>
+      </c>
+      <c r="L799">
+        <v>20260515</v>
+      </c>
+      <c r="M799" t="s">
+        <v>15</v>
+      </c>
+      <c r="N799" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="800" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A800" t="s">
+        <v>887</v>
+      </c>
+      <c r="B800" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C800" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D800" t="s">
+        <v>21</v>
+      </c>
+      <c r="E800" t="s">
+        <v>887</v>
+      </c>
+      <c r="F800" t="s">
+        <v>887</v>
+      </c>
+      <c r="G800" t="s">
+        <v>887</v>
+      </c>
+      <c r="H800" t="s">
+        <v>887</v>
+      </c>
+      <c r="I800">
+        <v>0</v>
+      </c>
+      <c r="J800" t="s">
+        <v>887</v>
+      </c>
+      <c r="K800" t="s">
+        <v>886</v>
+      </c>
+      <c r="L800" t="s">
+        <v>887</v>
+      </c>
+      <c r="M800" t="s">
+        <v>887</v>
+      </c>
+      <c r="N800" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="801" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A801" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B801" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C801" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D801" t="s">
+        <v>60</v>
+      </c>
+      <c r="E801" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F801" t="s">
+        <v>12</v>
+      </c>
+      <c r="G801" t="s">
+        <v>13</v>
+      </c>
+      <c r="H801">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I801">
+        <v>1</v>
+      </c>
+      <c r="L801">
+        <v>20260515</v>
+      </c>
+      <c r="M801" t="s">
+        <v>15</v>
+      </c>
+      <c r="N801" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="802" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A802" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B802" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C802" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D802" t="s">
+        <v>60</v>
+      </c>
+      <c r="E802" t="s">
+        <v>79</v>
+      </c>
+      <c r="F802" t="s">
+        <v>22</v>
+      </c>
+      <c r="G802" t="s">
+        <v>13</v>
+      </c>
+      <c r="H802">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I802">
+        <v>1</v>
+      </c>
+      <c r="L802">
+        <v>20260515</v>
+      </c>
+      <c r="M802" t="s">
+        <v>15</v>
+      </c>
+      <c r="N802" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="803" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A803" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C803" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D803" t="s">
+        <v>60</v>
+      </c>
+      <c r="E803" t="s">
+        <v>79</v>
+      </c>
+      <c r="F803" t="s">
+        <v>22</v>
+      </c>
+      <c r="G803" t="s">
+        <v>13</v>
+      </c>
+      <c r="H803">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="I803">
+        <v>1</v>
+      </c>
+      <c r="L803">
+        <v>20260515</v>
+      </c>
+      <c r="M803" t="s">
+        <v>15</v>
+      </c>
+      <c r="N803" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="804" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A804" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C804" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D804" t="s">
+        <v>60</v>
+      </c>
+      <c r="E804" t="s">
+        <v>79</v>
+      </c>
+      <c r="F804" t="s">
+        <v>22</v>
+      </c>
+      <c r="G804" t="s">
+        <v>13</v>
+      </c>
+      <c r="H804">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="I804">
+        <v>1</v>
+      </c>
+      <c r="L804">
+        <v>20260515</v>
+      </c>
+      <c r="M804" t="s">
+        <v>15</v>
+      </c>
+      <c r="N804" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="805" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A805" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C805" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D805" t="s">
+        <v>60</v>
+      </c>
+      <c r="E805" t="s">
+        <v>79</v>
+      </c>
+      <c r="F805" t="s">
+        <v>22</v>
+      </c>
+      <c r="G805" t="s">
+        <v>13</v>
+      </c>
+      <c r="H805">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I805">
+        <v>1</v>
+      </c>
+      <c r="L805">
+        <v>20260515</v>
+      </c>
+      <c r="M805" t="s">
+        <v>15</v>
+      </c>
+      <c r="N805" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="806" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A806" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C806" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D806" t="s">
+        <v>60</v>
+      </c>
+      <c r="E806" t="s">
+        <v>45</v>
+      </c>
+      <c r="F806" t="s">
+        <v>22</v>
+      </c>
+      <c r="G806" t="s">
+        <v>13</v>
+      </c>
+      <c r="H806">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="I806">
+        <v>1</v>
+      </c>
+      <c r="L806">
+        <v>20260515</v>
+      </c>
+      <c r="M806" t="s">
+        <v>15</v>
+      </c>
+      <c r="N806" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="807" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A807" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C807" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D807" t="s">
+        <v>60</v>
+      </c>
+      <c r="E807" t="s">
+        <v>45</v>
+      </c>
+      <c r="F807" t="s">
+        <v>22</v>
+      </c>
+      <c r="G807" t="s">
+        <v>13</v>
+      </c>
+      <c r="H807">
+        <v>9.4E-2</v>
+      </c>
+      <c r="I807">
+        <v>1</v>
+      </c>
+      <c r="L807">
+        <v>20260515</v>
+      </c>
+      <c r="M807" t="s">
+        <v>15</v>
+      </c>
+      <c r="N807" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="808" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A808" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B808" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C808" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D808" t="s">
+        <v>60</v>
+      </c>
+      <c r="E808" t="s">
+        <v>45</v>
+      </c>
+      <c r="F808" t="s">
+        <v>22</v>
+      </c>
+      <c r="G808" t="s">
+        <v>13</v>
+      </c>
+      <c r="H808">
+        <v>0.03</v>
+      </c>
+      <c r="I808">
+        <v>1</v>
+      </c>
+      <c r="L808">
+        <v>20260515</v>
+      </c>
+      <c r="M808" t="s">
+        <v>15</v>
+      </c>
+      <c r="N808" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="809" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A809" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C809" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D809" t="s">
+        <v>21</v>
+      </c>
+      <c r="E809" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F809" t="s">
+        <v>12</v>
+      </c>
+      <c r="G809" t="s">
+        <v>13</v>
+      </c>
+      <c r="H809">
+        <v>0.109</v>
+      </c>
+      <c r="I809">
+        <v>1</v>
+      </c>
+      <c r="L809">
+        <v>20260515</v>
+      </c>
+      <c r="M809" t="s">
+        <v>15</v>
+      </c>
+      <c r="N809" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="810" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A810" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C810" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D810" t="s">
+        <v>21</v>
+      </c>
+      <c r="E810" t="s">
+        <v>27</v>
+      </c>
+      <c r="F810" t="s">
+        <v>16</v>
+      </c>
+      <c r="G810" t="s">
+        <v>13</v>
+      </c>
+      <c r="H810">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I810">
+        <v>1</v>
+      </c>
+      <c r="L810">
+        <v>20260515</v>
+      </c>
+      <c r="M810" t="s">
+        <v>15</v>
+      </c>
+      <c r="N810" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="811" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A811" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C811" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D811" t="s">
+        <v>60</v>
+      </c>
+      <c r="E811" t="s">
+        <v>27</v>
+      </c>
+      <c r="F811" t="s">
+        <v>16</v>
+      </c>
+      <c r="G811" t="s">
+        <v>13</v>
+      </c>
+      <c r="H811">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I811">
+        <v>1</v>
+      </c>
+      <c r="L811">
+        <v>20260515</v>
+      </c>
+      <c r="M811" t="s">
+        <v>15</v>
+      </c>
+      <c r="N811" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="812" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A812" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C812" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D812" t="s">
+        <v>60</v>
+      </c>
+      <c r="E812" t="s">
+        <v>27</v>
+      </c>
+      <c r="F812" t="s">
+        <v>16</v>
+      </c>
+      <c r="G812" t="s">
+        <v>19</v>
+      </c>
+      <c r="H812">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I812">
+        <v>1</v>
+      </c>
+      <c r="L812">
+        <v>20260515</v>
+      </c>
+      <c r="M812" t="s">
+        <v>15</v>
+      </c>
+      <c r="N812" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A813" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C813" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D813" t="s">
+        <v>60</v>
+      </c>
+      <c r="E813" t="s">
+        <v>27</v>
+      </c>
+      <c r="F813" t="s">
+        <v>22</v>
+      </c>
+      <c r="G813" t="s">
+        <v>13</v>
+      </c>
+      <c r="H813">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I813">
+        <v>1</v>
+      </c>
+      <c r="L813">
+        <v>20260515</v>
+      </c>
+      <c r="M813" t="s">
+        <v>15</v>
+      </c>
+      <c r="N813" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="814" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A814" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B814" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C814" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D814" t="s">
+        <v>60</v>
+      </c>
+      <c r="E814" t="s">
+        <v>27</v>
+      </c>
+      <c r="F814" t="s">
+        <v>22</v>
+      </c>
+      <c r="G814" t="s">
+        <v>13</v>
+      </c>
+      <c r="H814">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="I814">
+        <v>1</v>
+      </c>
+      <c r="L814">
+        <v>20260515</v>
+      </c>
+      <c r="M814" t="s">
+        <v>15</v>
+      </c>
+      <c r="N814" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="815" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A815" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B815" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C815" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D815" t="s">
+        <v>60</v>
+      </c>
+      <c r="E815" t="s">
+        <v>79</v>
+      </c>
+      <c r="F815" t="s">
+        <v>22</v>
+      </c>
+      <c r="G815" t="s">
+        <v>13</v>
+      </c>
+      <c r="H815">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="I815">
+        <v>1</v>
+      </c>
+      <c r="L815">
+        <v>20260515</v>
+      </c>
+      <c r="M815" t="s">
+        <v>15</v>
+      </c>
+      <c r="N815" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A816" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C816" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D816" t="s">
+        <v>833</v>
+      </c>
+      <c r="E816" t="s">
+        <v>17</v>
+      </c>
+      <c r="F816" t="s">
+        <v>12</v>
+      </c>
+      <c r="G816" t="s">
+        <v>13</v>
+      </c>
+      <c r="H816">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="I816">
+        <v>1</v>
+      </c>
+      <c r="L816">
+        <v>20260515</v>
+      </c>
+      <c r="M816" t="s">
+        <v>15</v>
+      </c>
+      <c r="N816" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="817" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A817" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C817" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D817" t="s">
+        <v>833</v>
+      </c>
+      <c r="E817" t="s">
+        <v>17</v>
+      </c>
+      <c r="F817" t="s">
+        <v>12</v>
+      </c>
+      <c r="G817" t="s">
+        <v>13</v>
+      </c>
+      <c r="H817">
+        <v>0.161</v>
+      </c>
+      <c r="I817">
+        <v>1</v>
+      </c>
+      <c r="L817">
+        <v>20260515</v>
+      </c>
+      <c r="M817" t="s">
+        <v>15</v>
+      </c>
+      <c r="N817" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="818" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A818" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C818" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D818" t="s">
+        <v>833</v>
+      </c>
+      <c r="E818" t="s">
+        <v>17</v>
+      </c>
+      <c r="F818" t="s">
+        <v>12</v>
+      </c>
+      <c r="G818" t="s">
+        <v>13</v>
+      </c>
+      <c r="H818">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="I818">
+        <v>1</v>
+      </c>
+      <c r="L818">
+        <v>20260515</v>
+      </c>
+      <c r="M818" t="s">
+        <v>15</v>
+      </c>
+      <c r="N818" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="819" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A819" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C819" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D819" t="s">
+        <v>833</v>
+      </c>
+      <c r="E819" t="s">
+        <v>17</v>
+      </c>
+      <c r="F819" t="s">
+        <v>12</v>
+      </c>
+      <c r="G819" t="s">
+        <v>13</v>
+      </c>
+      <c r="H819">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="I819">
+        <v>1</v>
+      </c>
+      <c r="L819">
+        <v>20260515</v>
+      </c>
+      <c r="M819" t="s">
+        <v>15</v>
+      </c>
+      <c r="N819" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="820" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A820" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C820" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D820" t="s">
+        <v>833</v>
+      </c>
+      <c r="E820" t="s">
+        <v>17</v>
+      </c>
+      <c r="F820" t="s">
+        <v>12</v>
+      </c>
+      <c r="G820" t="s">
+        <v>13</v>
+      </c>
+      <c r="H820">
+        <v>0.17</v>
+      </c>
+      <c r="I820">
+        <v>1</v>
+      </c>
+      <c r="L820">
+        <v>20260515</v>
+      </c>
+      <c r="M820" t="s">
+        <v>15</v>
+      </c>
+      <c r="N820" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="821" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A821" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C821" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D821" t="s">
+        <v>833</v>
+      </c>
+      <c r="E821" t="s">
+        <v>17</v>
+      </c>
+      <c r="F821" t="s">
+        <v>12</v>
+      </c>
+      <c r="G821" t="s">
+        <v>13</v>
+      </c>
+      <c r="H821">
+        <v>0.184</v>
+      </c>
+      <c r="I821">
+        <v>1</v>
+      </c>
+      <c r="L821">
+        <v>20260515</v>
+      </c>
+      <c r="M821" t="s">
+        <v>15</v>
+      </c>
+      <c r="N821" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="822" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A822" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C822" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D822" t="s">
+        <v>833</v>
+      </c>
+      <c r="E822" t="s">
+        <v>17</v>
+      </c>
+      <c r="F822" t="s">
+        <v>12</v>
+      </c>
+      <c r="G822" t="s">
+        <v>13</v>
+      </c>
+      <c r="H822">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="I822">
+        <v>1</v>
+      </c>
+      <c r="L822">
+        <v>20260515</v>
+      </c>
+      <c r="M822" t="s">
+        <v>15</v>
+      </c>
+      <c r="N822" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="823" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A823" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C823" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D823" t="s">
+        <v>833</v>
+      </c>
+      <c r="E823" t="s">
+        <v>17</v>
+      </c>
+      <c r="F823" t="s">
+        <v>12</v>
+      </c>
+      <c r="G823" t="s">
+        <v>13</v>
+      </c>
+      <c r="H823">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I823">
+        <v>1</v>
+      </c>
+      <c r="L823">
+        <v>20260515</v>
+      </c>
+      <c r="M823" t="s">
+        <v>15</v>
+      </c>
+      <c r="N823" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="824" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A824" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C824" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D824" t="s">
+        <v>833</v>
+      </c>
+      <c r="E824" t="s">
+        <v>17</v>
+      </c>
+      <c r="F824" t="s">
+        <v>12</v>
+      </c>
+      <c r="G824" t="s">
+        <v>13</v>
+      </c>
+      <c r="H824">
+        <v>0.156</v>
+      </c>
+      <c r="I824">
+        <v>1</v>
+      </c>
+      <c r="L824">
+        <v>20260515</v>
+      </c>
+      <c r="M824" t="s">
+        <v>15</v>
+      </c>
+      <c r="N824" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="825" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A825" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C825" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D825" t="s">
+        <v>833</v>
+      </c>
+      <c r="E825" t="s">
+        <v>17</v>
+      </c>
+      <c r="F825" t="s">
+        <v>12</v>
+      </c>
+      <c r="G825" t="s">
+        <v>13</v>
+      </c>
+      <c r="H825">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="I825">
+        <v>1</v>
+      </c>
+      <c r="L825">
+        <v>20260515</v>
+      </c>
+      <c r="M825" t="s">
+        <v>15</v>
+      </c>
+      <c r="N825" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="826" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A826" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C826" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D826" t="s">
+        <v>833</v>
+      </c>
+      <c r="E826" t="s">
+        <v>17</v>
+      </c>
+      <c r="F826" t="s">
+        <v>12</v>
+      </c>
+      <c r="G826" t="s">
+        <v>13</v>
+      </c>
+      <c r="H826">
+        <v>0.152</v>
+      </c>
+      <c r="I826">
+        <v>1</v>
+      </c>
+      <c r="L826">
+        <v>20260515</v>
+      </c>
+      <c r="M826" t="s">
+        <v>15</v>
+      </c>
+      <c r="N826" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="827" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A827" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C827" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D827" t="s">
+        <v>833</v>
+      </c>
+      <c r="E827" t="s">
+        <v>17</v>
+      </c>
+      <c r="F827" t="s">
+        <v>12</v>
+      </c>
+      <c r="G827" t="s">
+        <v>13</v>
+      </c>
+      <c r="H827">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I827">
+        <v>1</v>
+      </c>
+      <c r="L827">
+        <v>20260515</v>
+      </c>
+      <c r="M827" t="s">
+        <v>15</v>
+      </c>
+      <c r="N827" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="828" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A828" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C828" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D828" t="s">
+        <v>833</v>
+      </c>
+      <c r="E828" t="s">
+        <v>17</v>
+      </c>
+      <c r="F828" t="s">
+        <v>12</v>
+      </c>
+      <c r="G828" t="s">
+        <v>13</v>
+      </c>
+      <c r="H828">
+        <v>0.156</v>
+      </c>
+      <c r="I828">
+        <v>1</v>
+      </c>
+      <c r="L828">
+        <v>20260515</v>
+      </c>
+      <c r="M828" t="s">
+        <v>15</v>
+      </c>
+      <c r="N828" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="829" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A829" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C829" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D829" t="s">
+        <v>833</v>
+      </c>
+      <c r="E829" t="s">
+        <v>17</v>
+      </c>
+      <c r="F829" t="s">
+        <v>12</v>
+      </c>
+      <c r="G829" t="s">
+        <v>13</v>
+      </c>
+      <c r="H829">
+        <v>0.157</v>
+      </c>
+      <c r="I829">
+        <v>1</v>
+      </c>
+      <c r="L829">
+        <v>20260515</v>
+      </c>
+      <c r="M829" t="s">
+        <v>15</v>
+      </c>
+      <c r="N829" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="830" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A830" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B830" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C830" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D830" t="s">
+        <v>833</v>
+      </c>
+      <c r="E830" t="s">
+        <v>17</v>
+      </c>
+      <c r="F830" t="s">
+        <v>12</v>
+      </c>
+      <c r="G830" t="s">
+        <v>19</v>
+      </c>
+      <c r="H830">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="I830">
+        <v>1</v>
+      </c>
+      <c r="L830">
+        <v>20260515</v>
+      </c>
+      <c r="M830" t="s">
+        <v>15</v>
+      </c>
+      <c r="N830" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="831" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A831" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B831" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C831" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D831" t="s">
+        <v>833</v>
+      </c>
+      <c r="E831" t="s">
+        <v>17</v>
+      </c>
+      <c r="F831" t="s">
+        <v>16</v>
+      </c>
+      <c r="G831" t="s">
+        <v>13</v>
+      </c>
+      <c r="H831">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="I831">
+        <v>1</v>
+      </c>
+      <c r="L831">
+        <v>20260515</v>
+      </c>
+      <c r="M831" t="s">
+        <v>15</v>
+      </c>
+      <c r="N831" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="832" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A832" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C832" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D832" t="s">
+        <v>833</v>
+      </c>
+      <c r="E832" t="s">
+        <v>17</v>
+      </c>
+      <c r="F832" t="s">
+        <v>16</v>
+      </c>
+      <c r="G832" t="s">
+        <v>19</v>
+      </c>
+      <c r="H832">
+        <v>0.11</v>
+      </c>
+      <c r="I832">
+        <v>1</v>
+      </c>
+      <c r="L832">
+        <v>20260515</v>
+      </c>
+      <c r="M832" t="s">
+        <v>15</v>
+      </c>
+      <c r="N832" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="833" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A833" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B833" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C833" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D833" t="s">
+        <v>833</v>
+      </c>
+      <c r="E833" t="s">
+        <v>45</v>
+      </c>
+      <c r="F833" t="s">
+        <v>22</v>
+      </c>
+      <c r="G833" t="s">
+        <v>13</v>
+      </c>
+      <c r="H833">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="I833">
+        <v>1</v>
+      </c>
+      <c r="L833">
+        <v>20260515</v>
+      </c>
+      <c r="M833" t="s">
+        <v>15</v>
+      </c>
+      <c r="N833" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="834" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A834" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B834" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C834" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D834" t="s">
+        <v>833</v>
+      </c>
+      <c r="E834" t="s">
+        <v>45</v>
+      </c>
+      <c r="F834" t="s">
+        <v>22</v>
+      </c>
+      <c r="G834" t="s">
+        <v>13</v>
+      </c>
+      <c r="H834">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I834">
+        <v>1</v>
+      </c>
+      <c r="L834">
+        <v>20260515</v>
+      </c>
+      <c r="M834" t="s">
+        <v>15</v>
+      </c>
+      <c r="N834" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="835" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A835" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B835" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C835" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D835" t="s">
+        <v>833</v>
+      </c>
+      <c r="E835" t="s">
+        <v>45</v>
+      </c>
+      <c r="F835" t="s">
+        <v>22</v>
+      </c>
+      <c r="G835" t="s">
+        <v>13</v>
+      </c>
+      <c r="H835">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="I835">
+        <v>1</v>
+      </c>
+      <c r="L835">
+        <v>20260515</v>
+      </c>
+      <c r="M835" t="s">
+        <v>15</v>
+      </c>
+      <c r="N835" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="836" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A836" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B836" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C836" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D836" t="s">
+        <v>833</v>
+      </c>
+      <c r="E836" t="s">
+        <v>45</v>
+      </c>
+      <c r="F836" t="s">
+        <v>22</v>
+      </c>
+      <c r="G836" t="s">
+        <v>13</v>
+      </c>
+      <c r="H836">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="I836">
+        <v>1</v>
+      </c>
+      <c r="L836">
+        <v>20260515</v>
+      </c>
+      <c r="M836" t="s">
+        <v>15</v>
+      </c>
+      <c r="N836" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="837" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A837" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B837" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C837" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D837" t="s">
+        <v>833</v>
+      </c>
+      <c r="E837" t="s">
+        <v>45</v>
+      </c>
+      <c r="F837" t="s">
+        <v>22</v>
+      </c>
+      <c r="G837" t="s">
+        <v>13</v>
+      </c>
+      <c r="H837">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I837">
+        <v>1</v>
+      </c>
+      <c r="L837">
+        <v>20260515</v>
+      </c>
+      <c r="M837" t="s">
+        <v>15</v>
+      </c>
+      <c r="N837" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="838" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A838" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B838" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C838" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D838" t="s">
+        <v>833</v>
+      </c>
+      <c r="E838" t="s">
+        <v>45</v>
+      </c>
+      <c r="F838" t="s">
+        <v>22</v>
+      </c>
+      <c r="G838" t="s">
+        <v>13</v>
+      </c>
+      <c r="H838">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I838">
+        <v>1</v>
+      </c>
+      <c r="L838">
+        <v>20260515</v>
+      </c>
+      <c r="M838" t="s">
+        <v>15</v>
+      </c>
+      <c r="N838" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="839" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A839" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B839" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C839" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D839" t="s">
+        <v>833</v>
+      </c>
+      <c r="E839" t="s">
+        <v>45</v>
+      </c>
+      <c r="F839" t="s">
+        <v>22</v>
+      </c>
+      <c r="G839" t="s">
+        <v>19</v>
+      </c>
+      <c r="H839">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="I839">
+        <v>1</v>
+      </c>
+      <c r="L839">
+        <v>20260515</v>
+      </c>
+      <c r="M839" t="s">
+        <v>15</v>
+      </c>
+      <c r="N839" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="840" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A840" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C840" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D840" t="s">
+        <v>833</v>
+      </c>
+      <c r="E840" t="s">
+        <v>45</v>
+      </c>
+      <c r="F840" t="s">
+        <v>22</v>
+      </c>
+      <c r="G840" t="s">
+        <v>19</v>
+      </c>
+      <c r="H840">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I840">
+        <v>1</v>
+      </c>
+      <c r="L840">
+        <v>20260515</v>
+      </c>
+      <c r="M840" t="s">
+        <v>15</v>
+      </c>
+      <c r="N840" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="841" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A841" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C841" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D841" t="s">
+        <v>833</v>
+      </c>
+      <c r="E841" t="s">
+        <v>45</v>
+      </c>
+      <c r="F841" t="s">
+        <v>46</v>
+      </c>
+      <c r="G841" t="s">
+        <v>19</v>
+      </c>
+      <c r="H841">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I841">
+        <v>1</v>
+      </c>
+      <c r="L841">
+        <v>20260515</v>
+      </c>
+      <c r="M841" t="s">
+        <v>15</v>
+      </c>
+      <c r="N841" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="842" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A842" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C842" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D842" t="s">
+        <v>833</v>
+      </c>
+      <c r="E842" t="s">
+        <v>45</v>
+      </c>
+      <c r="F842" t="s">
+        <v>46</v>
+      </c>
+      <c r="G842" t="s">
+        <v>19</v>
+      </c>
+      <c r="H842">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I842">
+        <v>1</v>
+      </c>
+      <c r="L842">
+        <v>20260515</v>
+      </c>
+      <c r="M842" t="s">
+        <v>15</v>
+      </c>
+      <c r="N842" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="843" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A843" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B843" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C843" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D843" t="s">
+        <v>833</v>
+      </c>
+      <c r="E843" t="s">
+        <v>18</v>
+      </c>
+      <c r="F843" t="s">
+        <v>12</v>
+      </c>
+      <c r="G843" t="s">
+        <v>13</v>
+      </c>
+      <c r="H843">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="I843">
+        <v>1</v>
+      </c>
+      <c r="L843">
+        <v>20260515</v>
+      </c>
+      <c r="M843" t="s">
+        <v>15</v>
+      </c>
+      <c r="N843" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="844" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A844" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B844" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C844" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D844" t="s">
+        <v>833</v>
+      </c>
+      <c r="E844" t="s">
+        <v>18</v>
+      </c>
+      <c r="F844" t="s">
+        <v>12</v>
+      </c>
+      <c r="G844" t="s">
+        <v>19</v>
+      </c>
+      <c r="H844">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="I844">
+        <v>1</v>
+      </c>
+      <c r="L844">
+        <v>20260515</v>
+      </c>
+      <c r="M844" t="s">
+        <v>15</v>
+      </c>
+      <c r="N844" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="845" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A845" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B845" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C845" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D845" t="s">
+        <v>833</v>
+      </c>
+      <c r="E845" t="s">
+        <v>17</v>
+      </c>
+      <c r="F845" t="s">
+        <v>12</v>
+      </c>
+      <c r="G845" t="s">
+        <v>13</v>
+      </c>
+      <c r="H845">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="I845">
+        <v>1</v>
+      </c>
+      <c r="L845">
+        <v>20260515</v>
+      </c>
+      <c r="M845" t="s">
+        <v>15</v>
+      </c>
+      <c r="N845" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="846" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A846" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C846" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D846" t="s">
+        <v>833</v>
+      </c>
+      <c r="E846" t="s">
+        <v>17</v>
+      </c>
+      <c r="F846" t="s">
+        <v>12</v>
+      </c>
+      <c r="G846" t="s">
+        <v>13</v>
+      </c>
+      <c r="H846">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I846">
+        <v>1</v>
+      </c>
+      <c r="L846">
+        <v>20260515</v>
+      </c>
+      <c r="M846" t="s">
+        <v>15</v>
+      </c>
+      <c r="N846" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="847" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A847" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C847" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D847" t="s">
+        <v>833</v>
+      </c>
+      <c r="E847" t="s">
+        <v>17</v>
+      </c>
+      <c r="F847" t="s">
+        <v>12</v>
+      </c>
+      <c r="G847" t="s">
+        <v>13</v>
+      </c>
+      <c r="H847">
+        <v>0.22</v>
+      </c>
+      <c r="I847">
+        <v>1</v>
+      </c>
+      <c r="L847">
+        <v>20260515</v>
+      </c>
+      <c r="M847" t="s">
+        <v>15</v>
+      </c>
+      <c r="N847" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="848" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A848" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C848" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D848" t="s">
+        <v>833</v>
+      </c>
+      <c r="E848" t="s">
+        <v>17</v>
+      </c>
+      <c r="F848" t="s">
+        <v>12</v>
+      </c>
+      <c r="G848" t="s">
+        <v>13</v>
+      </c>
+      <c r="H848">
+        <v>0.192</v>
+      </c>
+      <c r="I848">
+        <v>1</v>
+      </c>
+      <c r="L848">
+        <v>20260515</v>
+      </c>
+      <c r="M848" t="s">
+        <v>15</v>
+      </c>
+      <c r="N848" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="849" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A849" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C849" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D849" t="s">
+        <v>833</v>
+      </c>
+      <c r="E849" t="s">
+        <v>45</v>
+      </c>
+      <c r="F849" t="s">
+        <v>22</v>
+      </c>
+      <c r="G849" t="s">
+        <v>13</v>
+      </c>
+      <c r="H849">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="I849">
+        <v>1</v>
+      </c>
+      <c r="L849">
+        <v>20260515</v>
+      </c>
+      <c r="M849" t="s">
+        <v>15</v>
+      </c>
+      <c r="N849" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="850" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A850" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B850" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C850" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D850" t="s">
+        <v>833</v>
+      </c>
+      <c r="E850" t="s">
+        <v>45</v>
+      </c>
+      <c r="F850" t="s">
+        <v>22</v>
+      </c>
+      <c r="G850" t="s">
+        <v>13</v>
+      </c>
+      <c r="H850">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="I850">
+        <v>1</v>
+      </c>
+      <c r="L850">
+        <v>20260515</v>
+      </c>
+      <c r="M850" t="s">
+        <v>15</v>
+      </c>
+      <c r="N850" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="851" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A851" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B851" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C851" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D851" t="s">
+        <v>833</v>
+      </c>
+      <c r="E851" t="s">
+        <v>45</v>
+      </c>
+      <c r="F851" t="s">
+        <v>22</v>
+      </c>
+      <c r="G851" t="s">
+        <v>13</v>
+      </c>
+      <c r="H851">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="I851">
+        <v>1</v>
+      </c>
+      <c r="L851">
+        <v>20260515</v>
+      </c>
+      <c r="M851" t="s">
+        <v>15</v>
+      </c>
+      <c r="N851" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="852" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A852" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C852" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D852" t="s">
+        <v>833</v>
+      </c>
+      <c r="E852" t="s">
+        <v>45</v>
+      </c>
+      <c r="F852" t="s">
+        <v>22</v>
+      </c>
+      <c r="G852" t="s">
+        <v>13</v>
+      </c>
+      <c r="H852">
+        <v>0.106</v>
+      </c>
+      <c r="I852">
+        <v>1</v>
+      </c>
+      <c r="L852">
+        <v>20260515</v>
+      </c>
+      <c r="M852" t="s">
+        <v>15</v>
+      </c>
+      <c r="N852" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="853" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A853" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C853" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D853" t="s">
+        <v>833</v>
+      </c>
+      <c r="E853" t="s">
+        <v>45</v>
+      </c>
+      <c r="F853" t="s">
+        <v>22</v>
+      </c>
+      <c r="G853" t="s">
+        <v>13</v>
+      </c>
+      <c r="H853">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="I853">
+        <v>1</v>
+      </c>
+      <c r="L853">
+        <v>20260515</v>
+      </c>
+      <c r="M853" t="s">
+        <v>15</v>
+      </c>
+      <c r="N853" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="854" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A854" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C854" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D854" t="s">
+        <v>833</v>
+      </c>
+      <c r="E854" t="s">
+        <v>45</v>
+      </c>
+      <c r="F854" t="s">
+        <v>46</v>
+      </c>
+      <c r="G854" t="s">
+        <v>19</v>
+      </c>
+      <c r="H854">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="I854">
+        <v>1</v>
+      </c>
+      <c r="L854">
+        <v>20260515</v>
+      </c>
+      <c r="M854" t="s">
+        <v>15</v>
+      </c>
+      <c r="N854" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="855" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A855" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C855" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D855" t="s">
+        <v>833</v>
+      </c>
+      <c r="E855" t="s">
+        <v>45</v>
+      </c>
+      <c r="F855" t="s">
+        <v>46</v>
+      </c>
+      <c r="G855" t="s">
+        <v>19</v>
+      </c>
+      <c r="H855">
+        <v>0.152</v>
+      </c>
+      <c r="I855">
+        <v>1</v>
+      </c>
+      <c r="L855">
+        <v>20260515</v>
+      </c>
+      <c r="M855" t="s">
+        <v>15</v>
+      </c>
+      <c r="N855" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="856" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A856" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C856" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D856" t="s">
+        <v>833</v>
+      </c>
+      <c r="E856" t="s">
+        <v>45</v>
+      </c>
+      <c r="F856" t="s">
+        <v>46</v>
+      </c>
+      <c r="G856" t="s">
+        <v>19</v>
+      </c>
+      <c r="H856">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="I856">
+        <v>1</v>
+      </c>
+      <c r="L856">
+        <v>20260515</v>
+      </c>
+      <c r="M856" t="s">
+        <v>15</v>
+      </c>
+      <c r="N856" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="857" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A857" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C857" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D857" t="s">
+        <v>833</v>
+      </c>
+      <c r="E857" t="s">
+        <v>45</v>
+      </c>
+      <c r="F857" t="s">
+        <v>46</v>
+      </c>
+      <c r="G857" t="s">
+        <v>19</v>
+      </c>
+      <c r="H857">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I857">
+        <v>1</v>
+      </c>
+      <c r="L857">
+        <v>20260515</v>
+      </c>
+      <c r="M857" t="s">
+        <v>15</v>
+      </c>
+      <c r="N857" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="858" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A858" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C858" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D858" t="s">
+        <v>833</v>
+      </c>
+      <c r="E858" t="s">
+        <v>17</v>
+      </c>
+      <c r="F858" t="s">
+        <v>16</v>
+      </c>
+      <c r="G858" t="s">
+        <v>13</v>
+      </c>
+      <c r="H858">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="I858">
+        <v>1</v>
+      </c>
+      <c r="L858">
+        <v>20260515</v>
+      </c>
+      <c r="M858" t="s">
+        <v>15</v>
+      </c>
+      <c r="N858" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="859" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A859" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C859" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D859" t="s">
+        <v>833</v>
+      </c>
+      <c r="E859" t="s">
+        <v>17</v>
+      </c>
+      <c r="F859" t="s">
+        <v>16</v>
+      </c>
+      <c r="G859" t="s">
+        <v>13</v>
+      </c>
+      <c r="H859">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="I859">
+        <v>1</v>
+      </c>
+      <c r="L859">
+        <v>20260515</v>
+      </c>
+      <c r="M859" t="s">
+        <v>15</v>
+      </c>
+      <c r="N859" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="860" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A860" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C860" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D860" t="s">
+        <v>833</v>
+      </c>
+      <c r="E860" t="s">
+        <v>17</v>
+      </c>
+      <c r="F860" t="s">
+        <v>16</v>
+      </c>
+      <c r="G860" t="s">
+        <v>13</v>
+      </c>
+      <c r="H860">
+        <v>0.161</v>
+      </c>
+      <c r="I860">
+        <v>1</v>
+      </c>
+      <c r="L860">
+        <v>20260515</v>
+      </c>
+      <c r="M860" t="s">
+        <v>15</v>
+      </c>
+      <c r="N860" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="861" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A861" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C861" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D861" t="s">
+        <v>833</v>
+      </c>
+      <c r="E861" t="s">
+        <v>17</v>
+      </c>
+      <c r="F861" t="s">
+        <v>16</v>
+      </c>
+      <c r="G861" t="s">
+        <v>13</v>
+      </c>
+      <c r="H861">
+        <v>0.13</v>
+      </c>
+      <c r="I861">
+        <v>1</v>
+      </c>
+      <c r="L861">
+        <v>20260515</v>
+      </c>
+      <c r="M861" t="s">
+        <v>15</v>
+      </c>
+      <c r="N861" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="862" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A862" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C862" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D862" t="s">
+        <v>833</v>
+      </c>
+      <c r="E862" t="s">
+        <v>17</v>
+      </c>
+      <c r="F862" t="s">
+        <v>16</v>
+      </c>
+      <c r="G862" t="s">
+        <v>13</v>
+      </c>
+      <c r="H862">
+        <v>0.214</v>
+      </c>
+      <c r="I862">
+        <v>1</v>
+      </c>
+      <c r="L862">
+        <v>20260515</v>
+      </c>
+      <c r="M862" t="s">
+        <v>15</v>
+      </c>
+      <c r="N862" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="863" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A863" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C863" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D863" t="s">
+        <v>833</v>
+      </c>
+      <c r="E863" t="s">
+        <v>17</v>
+      </c>
+      <c r="F863" t="s">
+        <v>16</v>
+      </c>
+      <c r="G863" t="s">
+        <v>19</v>
+      </c>
+      <c r="H863">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="I863">
+        <v>1</v>
+      </c>
+      <c r="L863">
+        <v>20260515</v>
+      </c>
+      <c r="M863" t="s">
+        <v>15</v>
+      </c>
+      <c r="N863" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="864" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A864" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C864" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D864" t="s">
+        <v>833</v>
+      </c>
+      <c r="E864" t="s">
+        <v>45</v>
+      </c>
+      <c r="F864" t="s">
+        <v>22</v>
+      </c>
+      <c r="G864" t="s">
+        <v>19</v>
+      </c>
+      <c r="H864">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="I864">
+        <v>1</v>
+      </c>
+      <c r="L864">
+        <v>20260515</v>
+      </c>
+      <c r="M864" t="s">
+        <v>15</v>
+      </c>
+      <c r="N864" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="865" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A865" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C865" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D865" t="s">
+        <v>833</v>
+      </c>
+      <c r="E865" t="s">
+        <v>45</v>
+      </c>
+      <c r="F865" t="s">
+        <v>22</v>
+      </c>
+      <c r="G865" t="s">
+        <v>19</v>
+      </c>
+      <c r="H865">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="I865">
+        <v>1</v>
+      </c>
+      <c r="L865">
+        <v>20260515</v>
+      </c>
+      <c r="M865" t="s">
+        <v>15</v>
+      </c>
+      <c r="N865" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="866" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A866" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C866" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D866" t="s">
+        <v>833</v>
+      </c>
+      <c r="E866" t="s">
+        <v>45</v>
+      </c>
+      <c r="F866" t="s">
+        <v>46</v>
+      </c>
+      <c r="G866" t="s">
+        <v>19</v>
+      </c>
+      <c r="H866">
+        <v>0.05</v>
+      </c>
+      <c r="I866">
+        <v>1</v>
+      </c>
+      <c r="L866">
+        <v>20260515</v>
+      </c>
+      <c r="M866" t="s">
+        <v>15</v>
+      </c>
+      <c r="N866" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="867" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A867" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C867" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D867" t="s">
+        <v>833</v>
+      </c>
+      <c r="E867" t="s">
+        <v>45</v>
+      </c>
+      <c r="F867" t="s">
+        <v>46</v>
+      </c>
+      <c r="G867" t="s">
+        <v>19</v>
+      </c>
+      <c r="H867">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="I867">
+        <v>1</v>
+      </c>
+      <c r="L867">
+        <v>20260515</v>
+      </c>
+      <c r="M867" t="s">
+        <v>15</v>
+      </c>
+      <c r="N867" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="868" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A868" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C868" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D868" t="s">
+        <v>833</v>
+      </c>
+      <c r="E868" t="s">
+        <v>45</v>
+      </c>
+      <c r="F868" t="s">
+        <v>46</v>
+      </c>
+      <c r="G868" t="s">
+        <v>19</v>
+      </c>
+      <c r="H868">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I868">
+        <v>1</v>
+      </c>
+      <c r="L868">
+        <v>20260515</v>
+      </c>
+      <c r="M868" t="s">
+        <v>15</v>
+      </c>
+      <c r="N868" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="869" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A869" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C869" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D869" t="s">
+        <v>833</v>
+      </c>
+      <c r="E869" t="s">
+        <v>45</v>
+      </c>
+      <c r="F869" t="s">
+        <v>22</v>
+      </c>
+      <c r="G869" t="s">
+        <v>13</v>
+      </c>
+      <c r="H869">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="I869">
+        <v>1</v>
+      </c>
+      <c r="L869">
+        <v>20260515</v>
+      </c>
+      <c r="M869" t="s">
+        <v>15</v>
+      </c>
+      <c r="N869" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="870" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A870" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C870" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D870" t="s">
+        <v>833</v>
+      </c>
+      <c r="E870" t="s">
+        <v>45</v>
+      </c>
+      <c r="F870" t="s">
+        <v>22</v>
+      </c>
+      <c r="G870" t="s">
+        <v>13</v>
+      </c>
+      <c r="H870">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="I870">
+        <v>1</v>
+      </c>
+      <c r="L870">
+        <v>20260515</v>
+      </c>
+      <c r="M870" t="s">
+        <v>15</v>
+      </c>
+      <c r="N870" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="871" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A871" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C871" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D871" t="s">
+        <v>833</v>
+      </c>
+      <c r="E871" t="s">
+        <v>45</v>
+      </c>
+      <c r="F871" t="s">
+        <v>22</v>
+      </c>
+      <c r="G871" t="s">
+        <v>13</v>
+      </c>
+      <c r="H871">
+        <v>0.15</v>
+      </c>
+      <c r="I871">
+        <v>1</v>
+      </c>
+      <c r="L871">
+        <v>20260515</v>
+      </c>
+      <c r="M871" t="s">
+        <v>15</v>
+      </c>
+      <c r="N871" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="872" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A872" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C872" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D872" t="s">
+        <v>833</v>
+      </c>
+      <c r="E872" t="s">
+        <v>45</v>
+      </c>
+      <c r="F872" t="s">
+        <v>22</v>
+      </c>
+      <c r="G872" t="s">
+        <v>13</v>
+      </c>
+      <c r="H872">
+        <v>0.124</v>
+      </c>
+      <c r="I872">
+        <v>1</v>
+      </c>
+      <c r="L872">
+        <v>20260515</v>
+      </c>
+      <c r="M872" t="s">
+        <v>15</v>
+      </c>
+      <c r="N872" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="873" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A873" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C873" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D873" t="s">
+        <v>833</v>
+      </c>
+      <c r="E873" t="s">
+        <v>45</v>
+      </c>
+      <c r="F873" t="s">
+        <v>22</v>
+      </c>
+      <c r="G873" t="s">
+        <v>13</v>
+      </c>
+      <c r="H873">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I873">
+        <v>1</v>
+      </c>
+      <c r="L873">
+        <v>20260515</v>
+      </c>
+      <c r="M873" t="s">
+        <v>15</v>
+      </c>
+      <c r="N873" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="874" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A874" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C874" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D874" t="s">
+        <v>833</v>
+      </c>
+      <c r="E874" t="s">
+        <v>45</v>
+      </c>
+      <c r="F874" t="s">
+        <v>22</v>
+      </c>
+      <c r="G874" t="s">
+        <v>13</v>
+      </c>
+      <c r="H874">
+        <v>0.151</v>
+      </c>
+      <c r="I874">
+        <v>1</v>
+      </c>
+      <c r="L874">
+        <v>20260515</v>
+      </c>
+      <c r="M874" t="s">
+        <v>15</v>
+      </c>
+      <c r="N874" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="875" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A875" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C875" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D875" t="s">
+        <v>833</v>
+      </c>
+      <c r="E875" t="s">
+        <v>45</v>
+      </c>
+      <c r="F875" t="s">
+        <v>22</v>
+      </c>
+      <c r="G875" t="s">
+        <v>13</v>
+      </c>
+      <c r="H875">
+        <v>0.128</v>
+      </c>
+      <c r="I875">
+        <v>1</v>
+      </c>
+      <c r="L875">
+        <v>20260515</v>
+      </c>
+      <c r="M875" t="s">
+        <v>15</v>
+      </c>
+      <c r="N875" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="876" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A876" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C876" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D876" t="s">
+        <v>833</v>
+      </c>
+      <c r="E876" t="s">
+        <v>45</v>
+      </c>
+      <c r="F876" t="s">
+        <v>22</v>
+      </c>
+      <c r="G876" t="s">
+        <v>13</v>
+      </c>
+      <c r="H876">
+        <v>0.123</v>
+      </c>
+      <c r="I876">
+        <v>1</v>
+      </c>
+      <c r="L876">
+        <v>20260515</v>
+      </c>
+      <c r="M876" t="s">
+        <v>15</v>
+      </c>
+      <c r="N876" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="877" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A877" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C877" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D877" t="s">
+        <v>833</v>
+      </c>
+      <c r="E877" t="s">
+        <v>45</v>
+      </c>
+      <c r="F877" t="s">
+        <v>22</v>
+      </c>
+      <c r="G877" t="s">
+        <v>13</v>
+      </c>
+      <c r="H877">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I877">
+        <v>1</v>
+      </c>
+      <c r="L877">
+        <v>20260515</v>
+      </c>
+      <c r="M877" t="s">
+        <v>15</v>
+      </c>
+      <c r="N877" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="878" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A878" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C878" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D878" t="s">
+        <v>833</v>
+      </c>
+      <c r="E878" t="s">
+        <v>45</v>
+      </c>
+      <c r="F878" t="s">
+        <v>22</v>
+      </c>
+      <c r="G878" t="s">
+        <v>13</v>
+      </c>
+      <c r="H878">
+        <v>0.11</v>
+      </c>
+      <c r="I878">
+        <v>1</v>
+      </c>
+      <c r="L878">
+        <v>20260515</v>
+      </c>
+      <c r="M878" t="s">
+        <v>15</v>
+      </c>
+      <c r="N878" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="879" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A879" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C879" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D879" t="s">
+        <v>833</v>
+      </c>
+      <c r="E879" t="s">
+        <v>45</v>
+      </c>
+      <c r="F879" t="s">
+        <v>22</v>
+      </c>
+      <c r="G879" t="s">
+        <v>13</v>
+      </c>
+      <c r="H879">
+        <v>0.157</v>
+      </c>
+      <c r="I879">
+        <v>1</v>
+      </c>
+      <c r="L879">
+        <v>20260515</v>
+      </c>
+      <c r="M879" t="s">
+        <v>15</v>
+      </c>
+      <c r="N879" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="880" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A880" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C880" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D880" t="s">
+        <v>833</v>
+      </c>
+      <c r="E880" t="s">
+        <v>45</v>
+      </c>
+      <c r="F880" t="s">
+        <v>22</v>
+      </c>
+      <c r="G880" t="s">
+        <v>13</v>
+      </c>
+      <c r="H880">
+        <v>0.127</v>
+      </c>
+      <c r="I880">
+        <v>1</v>
+      </c>
+      <c r="L880">
+        <v>20260515</v>
+      </c>
+      <c r="M880" t="s">
+        <v>15</v>
+      </c>
+      <c r="N880" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="881" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A881" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C881" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D881" t="s">
+        <v>833</v>
+      </c>
+      <c r="E881" t="s">
+        <v>45</v>
+      </c>
+      <c r="F881" t="s">
+        <v>22</v>
+      </c>
+      <c r="G881" t="s">
+        <v>13</v>
+      </c>
+      <c r="H881">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I881">
+        <v>1</v>
+      </c>
+      <c r="L881">
+        <v>20260515</v>
+      </c>
+      <c r="M881" t="s">
+        <v>15</v>
+      </c>
+      <c r="N881" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="882" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A882" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C882" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D882" t="s">
+        <v>833</v>
+      </c>
+      <c r="E882" t="s">
+        <v>45</v>
+      </c>
+      <c r="F882" t="s">
+        <v>22</v>
+      </c>
+      <c r="G882" t="s">
+        <v>13</v>
+      </c>
+      <c r="H882">
+        <v>0.151</v>
+      </c>
+      <c r="I882">
+        <v>1</v>
+      </c>
+      <c r="L882">
+        <v>20260515</v>
+      </c>
+      <c r="M882" t="s">
+        <v>15</v>
+      </c>
+      <c r="N882" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="883" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A883" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C883" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D883" t="s">
+        <v>833</v>
+      </c>
+      <c r="E883" t="s">
+        <v>45</v>
+      </c>
+      <c r="F883" t="s">
+        <v>22</v>
+      </c>
+      <c r="G883" t="s">
+        <v>13</v>
+      </c>
+      <c r="H883">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I883">
+        <v>1</v>
+      </c>
+      <c r="L883">
+        <v>20260515</v>
+      </c>
+      <c r="M883" t="s">
+        <v>15</v>
+      </c>
+      <c r="N883" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="884" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A884" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C884" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D884" t="s">
+        <v>833</v>
+      </c>
+      <c r="E884" t="s">
+        <v>45</v>
+      </c>
+      <c r="F884" t="s">
+        <v>22</v>
+      </c>
+      <c r="G884" t="s">
+        <v>13</v>
+      </c>
+      <c r="H884">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I884">
+        <v>1</v>
+      </c>
+      <c r="L884">
+        <v>20260515</v>
+      </c>
+      <c r="M884" t="s">
+        <v>15</v>
+      </c>
+      <c r="N884" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="885" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A885" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C885" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D885" t="s">
+        <v>833</v>
+      </c>
+      <c r="E885" t="s">
+        <v>45</v>
+      </c>
+      <c r="F885" t="s">
+        <v>22</v>
+      </c>
+      <c r="G885" t="s">
+        <v>13</v>
+      </c>
+      <c r="H885">
+        <v>0.123</v>
+      </c>
+      <c r="I885">
+        <v>1</v>
+      </c>
+      <c r="L885">
+        <v>20260515</v>
+      </c>
+      <c r="M885" t="s">
+        <v>15</v>
+      </c>
+      <c r="N885" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="886" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A886" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C886" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D886" t="s">
+        <v>833</v>
+      </c>
+      <c r="E886" t="s">
+        <v>45</v>
+      </c>
+      <c r="F886" t="s">
+        <v>22</v>
+      </c>
+      <c r="G886" t="s">
+        <v>13</v>
+      </c>
+      <c r="H886">
+        <v>0.128</v>
+      </c>
+      <c r="I886">
+        <v>1</v>
+      </c>
+      <c r="L886">
+        <v>20260515</v>
+      </c>
+      <c r="M886" t="s">
+        <v>15</v>
+      </c>
+      <c r="N886" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="887" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A887" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C887" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D887" t="s">
+        <v>833</v>
+      </c>
+      <c r="E887" t="s">
+        <v>45</v>
+      </c>
+      <c r="F887" t="s">
+        <v>22</v>
+      </c>
+      <c r="G887" t="s">
+        <v>13</v>
+      </c>
+      <c r="H887">
+        <v>0.104</v>
+      </c>
+      <c r="I887">
+        <v>1</v>
+      </c>
+      <c r="L887">
+        <v>20260515</v>
+      </c>
+      <c r="M887" t="s">
+        <v>15</v>
+      </c>
+      <c r="N887" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="888" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A888" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C888" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D888" t="s">
+        <v>833</v>
+      </c>
+      <c r="E888" t="s">
+        <v>45</v>
+      </c>
+      <c r="F888" t="s">
+        <v>22</v>
+      </c>
+      <c r="G888" t="s">
+        <v>13</v>
+      </c>
+      <c r="H888">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I888">
+        <v>1</v>
+      </c>
+      <c r="L888">
+        <v>20260515</v>
+      </c>
+      <c r="M888" t="s">
+        <v>15</v>
+      </c>
+      <c r="N888" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="889" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A889" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C889" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D889" t="s">
+        <v>833</v>
+      </c>
+      <c r="E889" t="s">
+        <v>45</v>
+      </c>
+      <c r="F889" t="s">
+        <v>22</v>
+      </c>
+      <c r="G889" t="s">
+        <v>13</v>
+      </c>
+      <c r="H889">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="I889">
+        <v>1</v>
+      </c>
+      <c r="L889">
+        <v>20260515</v>
+      </c>
+      <c r="M889" t="s">
+        <v>15</v>
+      </c>
+      <c r="N889" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="890" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A890" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C890" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D890" t="s">
+        <v>833</v>
+      </c>
+      <c r="E890" t="s">
+        <v>45</v>
+      </c>
+      <c r="F890" t="s">
+        <v>22</v>
+      </c>
+      <c r="G890" t="s">
+        <v>13</v>
+      </c>
+      <c r="H890">
+        <v>0.161</v>
+      </c>
+      <c r="I890">
+        <v>1</v>
+      </c>
+      <c r="L890">
+        <v>20260515</v>
+      </c>
+      <c r="M890" t="s">
+        <v>15</v>
+      </c>
+      <c r="N890" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="891" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A891" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B891" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C891" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D891" t="s">
+        <v>833</v>
+      </c>
+      <c r="E891" t="s">
+        <v>45</v>
+      </c>
+      <c r="F891" t="s">
+        <v>22</v>
+      </c>
+      <c r="G891" t="s">
+        <v>13</v>
+      </c>
+      <c r="H891">
+        <v>0.129</v>
+      </c>
+      <c r="I891">
+        <v>1</v>
+      </c>
+      <c r="L891">
+        <v>20260515</v>
+      </c>
+      <c r="M891" t="s">
+        <v>15</v>
+      </c>
+      <c r="N891" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="892" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A892" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B892" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C892" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D892" t="s">
+        <v>833</v>
+      </c>
+      <c r="E892" t="s">
+        <v>45</v>
+      </c>
+      <c r="F892" t="s">
+        <v>22</v>
+      </c>
+      <c r="G892" t="s">
+        <v>13</v>
+      </c>
+      <c r="H892">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I892">
+        <v>1</v>
+      </c>
+      <c r="L892">
+        <v>20260515</v>
+      </c>
+      <c r="M892" t="s">
+        <v>15</v>
+      </c>
+      <c r="N892" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="893" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A893" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B893" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C893" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D893" t="s">
+        <v>833</v>
+      </c>
+      <c r="E893" t="s">
+        <v>45</v>
+      </c>
+      <c r="F893" t="s">
+        <v>22</v>
+      </c>
+      <c r="G893" t="s">
+        <v>13</v>
+      </c>
+      <c r="H893">
+        <v>0.02</v>
+      </c>
+      <c r="I893">
+        <v>1</v>
+      </c>
+      <c r="L893">
+        <v>20260515</v>
+      </c>
+      <c r="M893" t="s">
+        <v>15</v>
+      </c>
+      <c r="N893" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="894" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A894" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C894" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D894" t="s">
+        <v>833</v>
+      </c>
+      <c r="E894" t="s">
+        <v>45</v>
+      </c>
+      <c r="F894" t="s">
+        <v>22</v>
+      </c>
+      <c r="G894" t="s">
+        <v>13</v>
+      </c>
+      <c r="H894">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="I894">
+        <v>1</v>
+      </c>
+      <c r="J894" t="s">
+        <v>199</v>
+      </c>
+      <c r="L894">
+        <v>20260515</v>
+      </c>
+      <c r="M894" t="s">
+        <v>15</v>
+      </c>
+      <c r="N894" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="895" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A895" t="s">
+        <v>887</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C895" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D895" t="s">
+        <v>21</v>
+      </c>
+      <c r="E895" t="s">
+        <v>887</v>
+      </c>
+      <c r="F895" t="s">
+        <v>887</v>
+      </c>
+      <c r="G895" t="s">
+        <v>887</v>
+      </c>
+      <c r="H895" t="s">
+        <v>887</v>
+      </c>
+      <c r="I895">
+        <v>0</v>
+      </c>
+      <c r="J895" t="s">
+        <v>887</v>
+      </c>
+      <c r="K895" t="s">
+        <v>886</v>
+      </c>
+      <c r="L895" t="s">
+        <v>887</v>
+      </c>
+      <c r="M895" t="s">
+        <v>887</v>
+      </c>
+      <c r="N895" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="896" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A896" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C896" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D896" t="s">
+        <v>60</v>
+      </c>
+      <c r="E896" t="s">
+        <v>27</v>
+      </c>
+      <c r="F896" t="s">
+        <v>22</v>
+      </c>
+      <c r="G896" t="s">
+        <v>13</v>
+      </c>
+      <c r="H896">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="I896">
+        <v>1</v>
+      </c>
+      <c r="L896">
+        <v>20260515</v>
+      </c>
+      <c r="M896" t="s">
+        <v>15</v>
+      </c>
+      <c r="N896" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="897" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A897" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C897" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D897" t="s">
+        <v>60</v>
+      </c>
+      <c r="E897" t="s">
+        <v>27</v>
+      </c>
+      <c r="F897" t="s">
+        <v>22</v>
+      </c>
+      <c r="G897" t="s">
+        <v>13</v>
+      </c>
+      <c r="H897">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I897">
+        <v>1</v>
+      </c>
+      <c r="L897">
+        <v>20260515</v>
+      </c>
+      <c r="M897" t="s">
+        <v>15</v>
+      </c>
+      <c r="N897" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="898" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A898" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C898" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D898" t="s">
+        <v>60</v>
+      </c>
+      <c r="E898" t="s">
+        <v>79</v>
+      </c>
+      <c r="F898" t="s">
+        <v>22</v>
+      </c>
+      <c r="G898" t="s">
+        <v>13</v>
+      </c>
+      <c r="H898">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="I898">
+        <v>1</v>
+      </c>
+      <c r="L898">
+        <v>20260515</v>
+      </c>
+      <c r="M898" t="s">
+        <v>15</v>
+      </c>
+      <c r="N898" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="899" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A899" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C899" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D899" t="s">
+        <v>60</v>
+      </c>
+      <c r="E899" t="s">
+        <v>79</v>
+      </c>
+      <c r="F899" t="s">
+        <v>22</v>
+      </c>
+      <c r="G899" t="s">
+        <v>13</v>
+      </c>
+      <c r="H899">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I899">
+        <v>1</v>
+      </c>
+      <c r="L899">
+        <v>20260515</v>
+      </c>
+      <c r="M899" t="s">
+        <v>15</v>
+      </c>
+      <c r="N899" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="900" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A900" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B900" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C900" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D900" t="s">
+        <v>60</v>
+      </c>
+      <c r="E900" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F900" t="s">
+        <v>22</v>
+      </c>
+      <c r="G900" t="s">
+        <v>13</v>
+      </c>
+      <c r="H900">
+        <v>0.12</v>
+      </c>
+      <c r="I900">
+        <v>1</v>
+      </c>
+      <c r="L900">
+        <v>20260515</v>
+      </c>
+      <c r="M900" t="s">
+        <v>15</v>
+      </c>
+      <c r="N900" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="901" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A901" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B901" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C901" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D901" t="s">
+        <v>60</v>
+      </c>
+      <c r="E901" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F901" t="s">
+        <v>22</v>
+      </c>
+      <c r="G901" t="s">
+        <v>13</v>
+      </c>
+      <c r="H901">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="I901">
+        <v>1</v>
+      </c>
+      <c r="L901">
+        <v>20260515</v>
+      </c>
+      <c r="M901" t="s">
+        <v>15</v>
+      </c>
+      <c r="N901" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="902" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A902" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B902" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C902" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D902" t="s">
+        <v>60</v>
+      </c>
+      <c r="E902" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F902" t="s">
+        <v>46</v>
+      </c>
+      <c r="G902" t="s">
+        <v>19</v>
+      </c>
+      <c r="H902">
+        <v>2.3E-2</v>
+      </c>
+      <c r="I902">
+        <v>1</v>
+      </c>
+      <c r="L902">
+        <v>20260515</v>
+      </c>
+      <c r="M902" t="s">
+        <v>15</v>
+      </c>
+      <c r="N902" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="903" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A903" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B903" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C903" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D903" t="s">
+        <v>60</v>
+      </c>
+      <c r="E903" t="s">
+        <v>45</v>
+      </c>
+      <c r="F903" t="s">
+        <v>22</v>
+      </c>
+      <c r="G903" t="s">
+        <v>13</v>
+      </c>
+      <c r="H903">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I903">
+        <v>1</v>
+      </c>
+      <c r="J903" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L903">
+        <v>20260515</v>
+      </c>
+      <c r="M903" t="s">
+        <v>15</v>
+      </c>
+      <c r="N903" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="904" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A904" t="s">
+        <v>887</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C904" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D904" t="s">
+        <v>21</v>
+      </c>
+      <c r="E904" t="s">
+        <v>887</v>
+      </c>
+      <c r="F904" t="s">
+        <v>887</v>
+      </c>
+      <c r="G904" t="s">
+        <v>887</v>
+      </c>
+      <c r="H904" t="s">
+        <v>887</v>
+      </c>
+      <c r="I904">
+        <v>0</v>
+      </c>
+      <c r="J904" t="s">
+        <v>887</v>
+      </c>
+      <c r="K904" t="s">
+        <v>886</v>
+      </c>
+      <c r="L904" t="s">
+        <v>887</v>
+      </c>
+      <c r="M904" t="s">
+        <v>887</v>
+      </c>
+      <c r="N904" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="905" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A905" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C905" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D905" t="s">
+        <v>60</v>
+      </c>
+      <c r="E905" t="s">
+        <v>18</v>
+      </c>
+      <c r="F905" t="s">
+        <v>12</v>
+      </c>
+      <c r="G905" t="s">
+        <v>13</v>
+      </c>
+      <c r="H905">
+        <v>0.629</v>
+      </c>
+      <c r="I905">
+        <v>1</v>
+      </c>
+      <c r="L905">
+        <v>20260515</v>
+      </c>
+      <c r="M905" t="s">
+        <v>15</v>
+      </c>
+      <c r="N905" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="906" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A906" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C906" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D906" t="s">
+        <v>60</v>
+      </c>
+      <c r="E906" t="s">
+        <v>27</v>
+      </c>
+      <c r="F906" t="s">
+        <v>22</v>
+      </c>
+      <c r="G906" t="s">
+        <v>13</v>
+      </c>
+      <c r="H906">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I906">
+        <v>1</v>
+      </c>
+      <c r="L906">
+        <v>20260515</v>
+      </c>
+      <c r="M906" t="s">
+        <v>15</v>
+      </c>
+      <c r="N906" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="907" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A907" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C907" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D907" t="s">
+        <v>60</v>
+      </c>
+      <c r="E907" t="s">
+        <v>27</v>
+      </c>
+      <c r="F907" t="s">
+        <v>22</v>
+      </c>
+      <c r="G907" t="s">
+        <v>13</v>
+      </c>
+      <c r="H907">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I907">
+        <v>1</v>
+      </c>
+      <c r="L907">
+        <v>20260515</v>
+      </c>
+      <c r="M907" t="s">
+        <v>15</v>
+      </c>
+      <c r="N907" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="908" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A908" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C908" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D908" t="s">
+        <v>60</v>
+      </c>
+      <c r="E908" t="s">
+        <v>139</v>
+      </c>
+      <c r="F908" t="s">
+        <v>22</v>
+      </c>
+      <c r="G908" t="s">
+        <v>13</v>
+      </c>
+      <c r="H908">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="I908">
+        <v>1</v>
+      </c>
+      <c r="L908">
+        <v>20260515</v>
+      </c>
+      <c r="M908" t="s">
+        <v>15</v>
+      </c>
+      <c r="N908" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="909" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A909" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C909" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D909" t="s">
+        <v>60</v>
+      </c>
+      <c r="E909" t="s">
+        <v>79</v>
+      </c>
+      <c r="F909" t="s">
+        <v>22</v>
+      </c>
+      <c r="G909" t="s">
+        <v>13</v>
+      </c>
+      <c r="H909">
+        <v>0.372</v>
+      </c>
+      <c r="I909">
+        <v>1</v>
+      </c>
+      <c r="L909">
+        <v>20260515</v>
+      </c>
+      <c r="M909" t="s">
+        <v>15</v>
+      </c>
+      <c r="N909" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="910" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A910" t="s">
+        <v>887</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C910" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D910" t="s">
+        <v>21</v>
+      </c>
+      <c r="E910" t="s">
+        <v>887</v>
+      </c>
+      <c r="F910" t="s">
+        <v>887</v>
+      </c>
+      <c r="G910" t="s">
+        <v>887</v>
+      </c>
+      <c r="H910" t="s">
+        <v>887</v>
+      </c>
+      <c r="I910">
+        <v>0</v>
+      </c>
+      <c r="J910" t="s">
+        <v>887</v>
+      </c>
+      <c r="K910" t="s">
+        <v>886</v>
+      </c>
+      <c r="L910" t="s">
+        <v>887</v>
+      </c>
+      <c r="M910" t="s">
+        <v>887</v>
+      </c>
+      <c r="N910" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="911" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A911" t="s">
+        <v>887</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C911" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D911" t="s">
+        <v>60</v>
+      </c>
+      <c r="E911" t="s">
+        <v>887</v>
+      </c>
+      <c r="F911" t="s">
+        <v>887</v>
+      </c>
+      <c r="G911" t="s">
+        <v>887</v>
+      </c>
+      <c r="H911" t="s">
+        <v>887</v>
+      </c>
+      <c r="I911">
+        <v>0</v>
+      </c>
+      <c r="J911" t="s">
+        <v>887</v>
+      </c>
+      <c r="K911" t="s">
+        <v>886</v>
+      </c>
+      <c r="L911" t="s">
+        <v>887</v>
+      </c>
+      <c r="M911" t="s">
+        <v>887</v>
+      </c>
+      <c r="N911" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="912" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A912" t="s">
+        <v>887</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C912" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D912" t="s">
+        <v>21</v>
+      </c>
+      <c r="E912" t="s">
+        <v>887</v>
+      </c>
+      <c r="F912" t="s">
+        <v>887</v>
+      </c>
+      <c r="G912" t="s">
+        <v>887</v>
+      </c>
+      <c r="H912" t="s">
+        <v>887</v>
+      </c>
+      <c r="I912">
+        <v>0</v>
+      </c>
+      <c r="J912" t="s">
+        <v>887</v>
+      </c>
+      <c r="K912" t="s">
+        <v>886</v>
+      </c>
+      <c r="L912" t="s">
+        <v>887</v>
+      </c>
+      <c r="M912" t="s">
+        <v>887</v>
+      </c>
+      <c r="N912" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="913" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A913" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B913" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C913" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D913" t="s">
+        <v>60</v>
+      </c>
+      <c r="E913" t="s">
+        <v>27</v>
+      </c>
+      <c r="F913" t="s">
+        <v>22</v>
+      </c>
+      <c r="G913" t="s">
+        <v>13</v>
+      </c>
+      <c r="H913">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I913">
+        <v>1</v>
+      </c>
+      <c r="L913">
+        <v>20260515</v>
+      </c>
+      <c r="M913" t="s">
+        <v>15</v>
+      </c>
+      <c r="N913" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="914" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A914" t="s">
+        <v>887</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C914" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D914" t="s">
+        <v>21</v>
+      </c>
+      <c r="E914" t="s">
+        <v>887</v>
+      </c>
+      <c r="F914" t="s">
+        <v>887</v>
+      </c>
+      <c r="G914" t="s">
+        <v>887</v>
+      </c>
+      <c r="H914" t="s">
+        <v>887</v>
+      </c>
+      <c r="I914">
+        <v>0</v>
+      </c>
+      <c r="J914" t="s">
+        <v>887</v>
+      </c>
+      <c r="K914" t="s">
+        <v>886</v>
+      </c>
+      <c r="L914" t="s">
+        <v>887</v>
+      </c>
+      <c r="M914" t="s">
+        <v>887</v>
+      </c>
+      <c r="N914" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="915" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A915" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C915" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D915" t="s">
+        <v>60</v>
+      </c>
+      <c r="E915" t="s">
+        <v>27</v>
+      </c>
+      <c r="F915" t="s">
+        <v>22</v>
+      </c>
+      <c r="G915" t="s">
+        <v>13</v>
+      </c>
+      <c r="H915">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I915">
+        <v>1</v>
+      </c>
+      <c r="L915">
+        <v>20260515</v>
+      </c>
+      <c r="M915" t="s">
+        <v>15</v>
+      </c>
+      <c r="N915" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="916" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A916" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C916" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D916" t="s">
+        <v>60</v>
+      </c>
+      <c r="E916" t="s">
+        <v>27</v>
+      </c>
+      <c r="F916" t="s">
+        <v>22</v>
+      </c>
+      <c r="G916" t="s">
+        <v>13</v>
+      </c>
+      <c r="H916">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I916">
+        <v>1</v>
+      </c>
+      <c r="L916">
+        <v>20260515</v>
+      </c>
+      <c r="M916" t="s">
+        <v>15</v>
+      </c>
+      <c r="N916" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="917" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A917" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C917" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D917" t="s">
+        <v>60</v>
+      </c>
+      <c r="E917" t="s">
+        <v>27</v>
+      </c>
+      <c r="F917" t="s">
+        <v>22</v>
+      </c>
+      <c r="G917" t="s">
+        <v>13</v>
+      </c>
+      <c r="H917">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I917">
+        <v>1</v>
+      </c>
+      <c r="L917">
+        <v>20260515</v>
+      </c>
+      <c r="M917" t="s">
+        <v>15</v>
+      </c>
+      <c r="N917" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="918" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A918" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C918" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D918" t="s">
+        <v>60</v>
+      </c>
+      <c r="E918" t="s">
+        <v>27</v>
+      </c>
+      <c r="F918" t="s">
+        <v>22</v>
+      </c>
+      <c r="G918" t="s">
+        <v>13</v>
+      </c>
+      <c r="H918">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I918">
+        <v>1</v>
+      </c>
+      <c r="L918">
+        <v>20260515</v>
+      </c>
+      <c r="M918" t="s">
+        <v>15</v>
+      </c>
+      <c r="N918" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A919" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C919" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D919" t="s">
+        <v>60</v>
+      </c>
+      <c r="E919" t="s">
+        <v>79</v>
+      </c>
+      <c r="F919" t="s">
+        <v>22</v>
+      </c>
+      <c r="G919" t="s">
+        <v>13</v>
+      </c>
+      <c r="H919">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I919">
+        <v>1</v>
+      </c>
+      <c r="L919">
+        <v>20260515</v>
+      </c>
+      <c r="M919" t="s">
+        <v>15</v>
+      </c>
+      <c r="N919" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="920" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A920" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C920" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D920" t="s">
+        <v>21</v>
+      </c>
+      <c r="E920" t="s">
+        <v>139</v>
+      </c>
+      <c r="F920" t="s">
+        <v>12</v>
+      </c>
+      <c r="G920" t="s">
+        <v>13</v>
+      </c>
+      <c r="H920">
+        <v>0.111</v>
+      </c>
+      <c r="I920">
+        <v>1</v>
+      </c>
+      <c r="L920">
+        <v>20260515</v>
+      </c>
+      <c r="M920" t="s">
+        <v>15</v>
+      </c>
+      <c r="N920" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="921" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A921" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C921" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D921" t="s">
+        <v>60</v>
+      </c>
+      <c r="E921" t="s">
+        <v>79</v>
+      </c>
+      <c r="F921" t="s">
+        <v>22</v>
+      </c>
+      <c r="G921" t="s">
+        <v>13</v>
+      </c>
+      <c r="H921">
+        <v>1.73</v>
+      </c>
+      <c r="I921">
+        <v>1</v>
+      </c>
+      <c r="J921" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L921">
+        <v>20260515</v>
+      </c>
+      <c r="M921" t="s">
+        <v>15</v>
+      </c>
+      <c r="N921" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="922" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A922" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C922" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D922" t="s">
+        <v>60</v>
+      </c>
+      <c r="E922" t="s">
+        <v>27</v>
+      </c>
+      <c r="F922" t="s">
+        <v>22</v>
+      </c>
+      <c r="G922" t="s">
+        <v>13</v>
+      </c>
+      <c r="H922">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I922">
+        <v>1</v>
+      </c>
+      <c r="L922">
+        <v>20260515</v>
+      </c>
+      <c r="M922" t="s">
+        <v>15</v>
+      </c>
+      <c r="N922" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="923" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A923" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C923" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D923" t="s">
+        <v>833</v>
+      </c>
+      <c r="E923" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F923" t="s">
+        <v>12</v>
+      </c>
+      <c r="G923" t="s">
+        <v>13</v>
+      </c>
+      <c r="H923">
+        <v>0.315</v>
+      </c>
+      <c r="I923">
+        <v>1</v>
+      </c>
+      <c r="J923" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L923">
+        <v>20260515</v>
+      </c>
+      <c r="M923" t="s">
+        <v>15</v>
+      </c>
+      <c r="N923" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A924" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C924" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D924" t="s">
+        <v>833</v>
+      </c>
+      <c r="E924" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F924" t="s">
+        <v>12</v>
+      </c>
+      <c r="G924" t="s">
+        <v>13</v>
+      </c>
+      <c r="H924">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="I924">
+        <v>1</v>
+      </c>
+      <c r="J924" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L924">
+        <v>20260515</v>
+      </c>
+      <c r="M924" t="s">
+        <v>15</v>
+      </c>
+      <c r="N924" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="925" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A925" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C925" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D925" t="s">
+        <v>833</v>
+      </c>
+      <c r="E925" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F925" t="s">
+        <v>16</v>
+      </c>
+      <c r="G925" t="s">
+        <v>13</v>
+      </c>
+      <c r="H925">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="I925">
+        <v>1</v>
+      </c>
+      <c r="J925" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L925">
+        <v>20260515</v>
+      </c>
+      <c r="M925" t="s">
+        <v>15</v>
+      </c>
+      <c r="N925" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="926" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A926" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C926" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D926" t="s">
+        <v>833</v>
+      </c>
+      <c r="E926" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F926" t="s">
+        <v>46</v>
+      </c>
+      <c r="G926" t="s">
+        <v>19</v>
+      </c>
+      <c r="H926">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="I926">
+        <v>1</v>
+      </c>
+      <c r="L926">
+        <v>20260515</v>
+      </c>
+      <c r="M926" t="s">
+        <v>15</v>
+      </c>
+      <c r="N926" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="927" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A927" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C927" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D927" t="s">
+        <v>833</v>
+      </c>
+      <c r="E927" t="s">
+        <v>18</v>
+      </c>
+      <c r="F927" t="s">
+        <v>12</v>
+      </c>
+      <c r="G927" t="s">
+        <v>13</v>
+      </c>
+      <c r="H927">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="I927">
+        <v>1</v>
+      </c>
+      <c r="L927">
+        <v>20260515</v>
+      </c>
+      <c r="M927" t="s">
+        <v>15</v>
+      </c>
+      <c r="N927" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A928" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C928" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D928" t="s">
+        <v>833</v>
+      </c>
+      <c r="E928" t="s">
+        <v>18</v>
+      </c>
+      <c r="F928" t="s">
+        <v>12</v>
+      </c>
+      <c r="G928" t="s">
+        <v>13</v>
+      </c>
+      <c r="H928">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="I928">
+        <v>1</v>
+      </c>
+      <c r="L928">
+        <v>20260515</v>
+      </c>
+      <c r="M928" t="s">
+        <v>15</v>
+      </c>
+      <c r="N928" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="929" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A929" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C929" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D929" t="s">
+        <v>833</v>
+      </c>
+      <c r="E929" t="s">
+        <v>18</v>
+      </c>
+      <c r="F929" t="s">
+        <v>12</v>
+      </c>
+      <c r="G929" t="s">
+        <v>13</v>
+      </c>
+      <c r="H929">
+        <v>1.008</v>
+      </c>
+      <c r="I929">
+        <v>1</v>
+      </c>
+      <c r="L929">
+        <v>20260515</v>
+      </c>
+      <c r="M929" t="s">
+        <v>15</v>
+      </c>
+      <c r="N929" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="930" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A930" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B930" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C930" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D930" t="s">
+        <v>833</v>
+      </c>
+      <c r="E930" t="s">
+        <v>18</v>
+      </c>
+      <c r="F930" t="s">
+        <v>12</v>
+      </c>
+      <c r="G930" t="s">
+        <v>13</v>
+      </c>
+      <c r="H930">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="I930">
+        <v>1</v>
+      </c>
+      <c r="J930" t="s">
+        <v>107</v>
+      </c>
+      <c r="L930">
+        <v>20260515</v>
+      </c>
+      <c r="M930" t="s">
+        <v>15</v>
+      </c>
+      <c r="N930" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="931" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A931" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B931" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C931" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D931" t="s">
+        <v>833</v>
+      </c>
+      <c r="E931" t="s">
+        <v>79</v>
+      </c>
+      <c r="F931" t="s">
+        <v>22</v>
+      </c>
+      <c r="G931" t="s">
+        <v>13</v>
+      </c>
+      <c r="H931">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="I931">
+        <v>1</v>
+      </c>
+      <c r="L931">
+        <v>20260515</v>
+      </c>
+      <c r="M931" t="s">
+        <v>15</v>
+      </c>
+      <c r="N931" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="932" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A932" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B932" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C932" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D932" t="s">
+        <v>833</v>
+      </c>
+      <c r="E932" t="s">
+        <v>79</v>
+      </c>
+      <c r="F932" t="s">
+        <v>22</v>
+      </c>
+      <c r="G932" t="s">
+        <v>13</v>
+      </c>
+      <c r="H932">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="I932">
+        <v>1</v>
+      </c>
+      <c r="L932">
+        <v>20260515</v>
+      </c>
+      <c r="M932" t="s">
+        <v>15</v>
+      </c>
+      <c r="N932" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="933" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A933" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B933" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C933" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D933" t="s">
+        <v>833</v>
+      </c>
+      <c r="E933" t="s">
+        <v>79</v>
+      </c>
+      <c r="F933" t="s">
+        <v>22</v>
+      </c>
+      <c r="G933" t="s">
+        <v>13</v>
+      </c>
+      <c r="H933">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I933">
+        <v>1</v>
+      </c>
+      <c r="L933">
+        <v>20260515</v>
+      </c>
+      <c r="M933" t="s">
+        <v>15</v>
+      </c>
+      <c r="N933" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="934" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A934" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C934" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D934" t="s">
+        <v>833</v>
+      </c>
+      <c r="E934" t="s">
+        <v>45</v>
+      </c>
+      <c r="F934" t="s">
+        <v>22</v>
+      </c>
+      <c r="G934" t="s">
+        <v>13</v>
+      </c>
+      <c r="H934">
+        <v>0.127</v>
+      </c>
+      <c r="I934">
+        <v>1</v>
+      </c>
+      <c r="L934">
+        <v>20260515</v>
+      </c>
+      <c r="M934" t="s">
+        <v>15</v>
+      </c>
+      <c r="N934" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="935" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A935" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C935" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D935" t="s">
+        <v>833</v>
+      </c>
+      <c r="E935" t="s">
+        <v>45</v>
+      </c>
+      <c r="F935" t="s">
+        <v>22</v>
+      </c>
+      <c r="G935" t="s">
+        <v>13</v>
+      </c>
+      <c r="H935">
+        <v>0.753</v>
+      </c>
+      <c r="I935">
+        <v>1</v>
+      </c>
+      <c r="L935">
+        <v>20260515</v>
+      </c>
+      <c r="M935" t="s">
+        <v>15</v>
+      </c>
+      <c r="N935" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="936" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A936" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C936" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D936" t="s">
+        <v>833</v>
+      </c>
+      <c r="E936" t="s">
+        <v>45</v>
+      </c>
+      <c r="F936" t="s">
+        <v>46</v>
+      </c>
+      <c r="G936" t="s">
+        <v>19</v>
+      </c>
+      <c r="H936">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="I936">
+        <v>1</v>
+      </c>
+      <c r="L936">
+        <v>20260515</v>
+      </c>
+      <c r="M936" t="s">
+        <v>15</v>
+      </c>
+      <c r="N936" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="937" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A937" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C937" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D937" t="s">
+        <v>833</v>
+      </c>
+      <c r="E937" t="s">
+        <v>45</v>
+      </c>
+      <c r="F937" t="s">
+        <v>46</v>
+      </c>
+      <c r="G937" t="s">
+        <v>19</v>
+      </c>
+      <c r="H937">
+        <v>0.15</v>
+      </c>
+      <c r="I937">
+        <v>1</v>
+      </c>
+      <c r="L937">
+        <v>20260515</v>
+      </c>
+      <c r="M937" t="s">
+        <v>15</v>
+      </c>
+      <c r="N937" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="938" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A938" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C938" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D938" t="s">
+        <v>833</v>
+      </c>
+      <c r="E938" t="s">
+        <v>45</v>
+      </c>
+      <c r="F938" t="s">
+        <v>46</v>
+      </c>
+      <c r="G938" t="s">
+        <v>19</v>
+      </c>
+      <c r="H938">
+        <v>0.19</v>
+      </c>
+      <c r="I938">
+        <v>1</v>
+      </c>
+      <c r="L938">
+        <v>20260515</v>
+      </c>
+      <c r="M938" t="s">
+        <v>15</v>
+      </c>
+      <c r="N938" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="939" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A939" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C939" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D939" t="s">
+        <v>833</v>
+      </c>
+      <c r="E939" t="s">
+        <v>45</v>
+      </c>
+      <c r="F939" t="s">
+        <v>46</v>
+      </c>
+      <c r="G939" t="s">
+        <v>19</v>
+      </c>
+      <c r="H939">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I939">
+        <v>1</v>
+      </c>
+      <c r="L939">
+        <v>20260515</v>
+      </c>
+      <c r="M939" t="s">
+        <v>15</v>
+      </c>
+      <c r="N939" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="940" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A940" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C940" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D940" t="s">
+        <v>833</v>
+      </c>
+      <c r="E940" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F940" t="s">
+        <v>12</v>
+      </c>
+      <c r="G940" t="s">
+        <v>13</v>
+      </c>
+      <c r="H940">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="I940">
+        <v>1</v>
+      </c>
+      <c r="J940" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L940">
+        <v>20260515</v>
+      </c>
+      <c r="M940" t="s">
+        <v>15</v>
+      </c>
+      <c r="N940" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="941" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A941" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C941" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D941" t="s">
+        <v>833</v>
+      </c>
+      <c r="E941" t="s">
+        <v>18</v>
+      </c>
+      <c r="F941" t="s">
+        <v>12</v>
+      </c>
+      <c r="G941" t="s">
+        <v>13</v>
+      </c>
+      <c r="H941">
+        <v>1.1180000000000001</v>
+      </c>
+      <c r="I941">
+        <v>1</v>
+      </c>
+      <c r="L941">
+        <v>20260515</v>
+      </c>
+      <c r="M941" t="s">
+        <v>15</v>
+      </c>
+      <c r="N941" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="942" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A942" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C942" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D942" t="s">
+        <v>833</v>
+      </c>
+      <c r="E942" t="s">
+        <v>18</v>
+      </c>
+      <c r="F942" t="s">
+        <v>12</v>
+      </c>
+      <c r="G942" t="s">
+        <v>13</v>
+      </c>
+      <c r="H942">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="I942">
+        <v>1</v>
+      </c>
+      <c r="J942" t="s">
+        <v>107</v>
+      </c>
+      <c r="L942">
+        <v>20260515</v>
+      </c>
+      <c r="M942" t="s">
+        <v>15</v>
+      </c>
+      <c r="N942" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="943" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A943" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C943" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D943" t="s">
+        <v>833</v>
+      </c>
+      <c r="E943" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F943" t="s">
+        <v>22</v>
+      </c>
+      <c r="G943" t="s">
+        <v>13</v>
+      </c>
+      <c r="H943">
+        <v>0.02</v>
+      </c>
+      <c r="I943">
+        <v>1</v>
+      </c>
+      <c r="L943">
+        <v>20260515</v>
+      </c>
+      <c r="M943" t="s">
+        <v>15</v>
+      </c>
+      <c r="N943" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="944" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A944" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C944" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D944" t="s">
+        <v>833</v>
+      </c>
+      <c r="E944" t="s">
+        <v>27</v>
+      </c>
+      <c r="F944" t="s">
+        <v>22</v>
+      </c>
+      <c r="G944" t="s">
+        <v>13</v>
+      </c>
+      <c r="H944">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="I944">
+        <v>1</v>
+      </c>
+      <c r="L944">
+        <v>20260515</v>
+      </c>
+      <c r="M944" t="s">
+        <v>15</v>
+      </c>
+      <c r="N944" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="945" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A945" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C945" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D945" t="s">
+        <v>833</v>
+      </c>
+      <c r="E945" t="s">
+        <v>45</v>
+      </c>
+      <c r="F945" t="s">
+        <v>46</v>
+      </c>
+      <c r="G945" t="s">
+        <v>19</v>
+      </c>
+      <c r="H945">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I945">
+        <v>1</v>
+      </c>
+      <c r="L945">
+        <v>20260515</v>
+      </c>
+      <c r="M945" t="s">
+        <v>15</v>
+      </c>
+      <c r="N945" t="s">
         <v>25</v>
       </c>
     </row>
